--- a/reports/latest/Security_Test_Report.xlsx
+++ b/reports/latest/Security_Test_Report.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E456"/>
+  <dimension ref="A1:E468"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,10 +427,10 @@
         <v>Passed</v>
       </c>
       <c r="D2">
-        <v>0.32</v>
+        <v>0.71</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-30T13:03:26.515Z</v>
+        <v>2026-07-30T13:20:26.720Z</v>
       </c>
     </row>
     <row r="3">
@@ -444,10 +444,10 @@
         <v>Passed</v>
       </c>
       <c r="D3">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-30T13:03:27.515Z</v>
+        <v>2026-07-30T13:20:27.720Z</v>
       </c>
     </row>
     <row r="4">
@@ -461,10 +461,10 @@
         <v>Passed</v>
       </c>
       <c r="D4">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-30T13:03:28.515Z</v>
+        <v>2026-07-30T13:20:28.720Z</v>
       </c>
     </row>
     <row r="5">
@@ -478,10 +478,10 @@
         <v>Passed</v>
       </c>
       <c r="D5">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-30T13:03:29.515Z</v>
+        <v>2026-07-30T13:20:29.720Z</v>
       </c>
     </row>
     <row r="6">
@@ -495,10 +495,10 @@
         <v>Passed</v>
       </c>
       <c r="D6">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-30T13:03:30.515Z</v>
+        <v>2026-07-30T13:20:30.720Z</v>
       </c>
     </row>
     <row r="7">
@@ -512,10 +512,10 @@
         <v>Passed</v>
       </c>
       <c r="D7">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-30T13:03:31.515Z</v>
+        <v>2026-07-30T13:20:31.720Z</v>
       </c>
     </row>
     <row r="8">
@@ -529,10 +529,10 @@
         <v>Passed</v>
       </c>
       <c r="D8">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-30T13:03:32.515Z</v>
+        <v>2026-07-30T13:20:32.720Z</v>
       </c>
     </row>
     <row r="9">
@@ -546,10 +546,10 @@
         <v>Passed</v>
       </c>
       <c r="D9">
-        <v>0.22</v>
+        <v>1.47</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-30T13:03:33.515Z</v>
+        <v>2026-07-30T13:20:33.720Z</v>
       </c>
     </row>
     <row r="10">
@@ -563,10 +563,10 @@
         <v>Passed</v>
       </c>
       <c r="D10">
-        <v>1.85</v>
+        <v>0.77</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-30T13:03:34.515Z</v>
+        <v>2026-07-30T13:20:34.720Z</v>
       </c>
     </row>
     <row r="11">
@@ -580,10 +580,10 @@
         <v>Passed</v>
       </c>
       <c r="D11">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-30T13:03:35.515Z</v>
+        <v>2026-07-30T13:20:35.720Z</v>
       </c>
     </row>
     <row r="12">
@@ -597,10 +597,10 @@
         <v>Passed</v>
       </c>
       <c r="D12">
-        <v>0.64</v>
+        <v>1.15</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-30T13:03:36.515Z</v>
+        <v>2026-07-30T13:20:36.720Z</v>
       </c>
     </row>
     <row r="13">
@@ -614,10 +614,10 @@
         <v>Passed</v>
       </c>
       <c r="D13">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-30T13:03:37.515Z</v>
+        <v>2026-07-30T13:20:37.720Z</v>
       </c>
     </row>
     <row r="14">
@@ -631,10 +631,10 @@
         <v>Passed</v>
       </c>
       <c r="D14">
-        <v>0.59</v>
+        <v>1.13</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-30T13:03:38.515Z</v>
+        <v>2026-07-30T13:20:38.720Z</v>
       </c>
     </row>
     <row r="15">
@@ -648,10 +648,10 @@
         <v>Passed</v>
       </c>
       <c r="D15">
-        <v>1.97</v>
+        <v>1.05</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-30T13:03:39.515Z</v>
+        <v>2026-07-30T13:20:39.720Z</v>
       </c>
     </row>
     <row r="16">
@@ -665,10 +665,10 @@
         <v>Passed</v>
       </c>
       <c r="D16">
-        <v>1.03</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-30T13:03:40.515Z</v>
+        <v>2026-07-30T13:20:40.720Z</v>
       </c>
     </row>
     <row r="17">
@@ -682,10 +682,10 @@
         <v>Passed</v>
       </c>
       <c r="D17">
-        <v>1.96</v>
+        <v>0.2</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-30T13:03:41.515Z</v>
+        <v>2026-07-30T13:20:41.720Z</v>
       </c>
     </row>
     <row r="18">
@@ -699,10 +699,10 @@
         <v>Passed</v>
       </c>
       <c r="D18">
-        <v>0.4</v>
+        <v>1.92</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-30T13:03:42.515Z</v>
+        <v>2026-07-30T13:20:42.720Z</v>
       </c>
     </row>
     <row r="19">
@@ -716,10 +716,10 @@
         <v>Passed</v>
       </c>
       <c r="D19">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-30T13:03:43.515Z</v>
+        <v>2026-07-30T13:20:43.720Z</v>
       </c>
     </row>
     <row r="20">
@@ -733,10 +733,10 @@
         <v>Passed</v>
       </c>
       <c r="D20">
-        <v>1.24</v>
+        <v>0.8</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-30T13:03:44.515Z</v>
+        <v>2026-07-30T13:20:44.720Z</v>
       </c>
     </row>
     <row r="21">
@@ -750,10 +750,10 @@
         <v>Passed</v>
       </c>
       <c r="D21">
-        <v>0.42</v>
+        <v>1.14</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-30T13:03:45.515Z</v>
+        <v>2026-07-30T13:20:45.720Z</v>
       </c>
     </row>
     <row r="22">
@@ -767,10 +767,10 @@
         <v>Passed</v>
       </c>
       <c r="D22">
-        <v>0.27</v>
+        <v>1.42</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-30T13:03:46.515Z</v>
+        <v>2026-07-30T13:20:46.720Z</v>
       </c>
     </row>
     <row r="23">
@@ -784,10 +784,10 @@
         <v>Passed</v>
       </c>
       <c r="D23">
-        <v>1.6</v>
+        <v>0.02</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-30T13:03:47.515Z</v>
+        <v>2026-07-30T13:20:47.720Z</v>
       </c>
     </row>
     <row r="24">
@@ -801,10 +801,10 @@
         <v>Passed</v>
       </c>
       <c r="D24">
-        <v>1.12</v>
+        <v>0.48</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-30T13:03:48.515Z</v>
+        <v>2026-07-30T13:20:48.720Z</v>
       </c>
     </row>
     <row r="25">
@@ -818,10 +818,10 @@
         <v>Passed</v>
       </c>
       <c r="D25">
-        <v>0.51</v>
+        <v>1.51</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-30T13:03:49.515Z</v>
+        <v>2026-07-30T13:20:49.720Z</v>
       </c>
     </row>
     <row r="26">
@@ -835,10 +835,10 @@
         <v>Passed</v>
       </c>
       <c r="D26">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-30T13:03:50.515Z</v>
+        <v>2026-07-30T13:20:50.720Z</v>
       </c>
     </row>
     <row r="27">
@@ -852,10 +852,10 @@
         <v>Passed</v>
       </c>
       <c r="D27">
-        <v>0.29</v>
+        <v>1.32</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-30T13:03:51.515Z</v>
+        <v>2026-07-30T13:20:51.720Z</v>
       </c>
     </row>
     <row r="28">
@@ -869,10 +869,10 @@
         <v>Passed</v>
       </c>
       <c r="D28">
-        <v>0.15</v>
+        <v>1.47</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-30T13:03:52.515Z</v>
+        <v>2026-07-30T13:20:52.720Z</v>
       </c>
     </row>
     <row r="29">
@@ -886,10 +886,10 @@
         <v>Passed</v>
       </c>
       <c r="D29">
-        <v>0.78</v>
+        <v>1.87</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-30T13:03:53.515Z</v>
+        <v>2026-07-30T13:20:53.720Z</v>
       </c>
     </row>
     <row r="30">
@@ -903,10 +903,10 @@
         <v>Passed</v>
       </c>
       <c r="D30">
-        <v>1.13</v>
+        <v>0.26</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-30T13:03:54.515Z</v>
+        <v>2026-07-30T13:20:54.720Z</v>
       </c>
     </row>
     <row r="31">
@@ -920,10 +920,10 @@
         <v>Passed</v>
       </c>
       <c r="D31">
-        <v>0.09</v>
+        <v>0.87</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-30T13:03:55.515Z</v>
+        <v>2026-07-30T13:20:55.720Z</v>
       </c>
     </row>
     <row r="32">
@@ -937,10 +937,10 @@
         <v>Passed</v>
       </c>
       <c r="D32">
-        <v>0.02</v>
+        <v>1.11</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-30T13:03:56.515Z</v>
+        <v>2026-07-30T13:20:56.720Z</v>
       </c>
     </row>
     <row r="33">
@@ -954,10 +954,10 @@
         <v>Passed</v>
       </c>
       <c r="D33">
-        <v>1.13</v>
+        <v>2</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-30T13:03:57.515Z</v>
+        <v>2026-07-30T13:20:57.720Z</v>
       </c>
     </row>
     <row r="34">
@@ -971,10 +971,10 @@
         <v>Passed</v>
       </c>
       <c r="D34">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-30T13:03:58.515Z</v>
+        <v>2026-07-30T13:20:58.720Z</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>Passed</v>
       </c>
       <c r="D35">
-        <v>0.94</v>
+        <v>0.77</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-30T13:03:59.515Z</v>
+        <v>2026-07-30T13:20:59.720Z</v>
       </c>
     </row>
     <row r="36">
@@ -1005,10 +1005,10 @@
         <v>Passed</v>
       </c>
       <c r="D36">
-        <v>0.05</v>
+        <v>1.17</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-30T13:04:00.515Z</v>
+        <v>2026-07-30T13:21:00.720Z</v>
       </c>
     </row>
     <row r="37">
@@ -1022,10 +1022,10 @@
         <v>Passed</v>
       </c>
       <c r="D37">
-        <v>0.34</v>
+        <v>1.49</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-30T13:04:01.515Z</v>
+        <v>2026-07-30T13:21:01.720Z</v>
       </c>
     </row>
     <row r="38">
@@ -1039,10 +1039,10 @@
         <v>Passed</v>
       </c>
       <c r="D38">
-        <v>0.28</v>
+        <v>0.06</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-30T13:04:02.515Z</v>
+        <v>2026-07-30T13:21:02.720Z</v>
       </c>
     </row>
     <row r="39">
@@ -1056,10 +1056,10 @@
         <v>Passed</v>
       </c>
       <c r="D39">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-30T13:04:03.515Z</v>
+        <v>2026-07-30T13:21:03.720Z</v>
       </c>
     </row>
     <row r="40">
@@ -1073,10 +1073,10 @@
         <v>Passed</v>
       </c>
       <c r="D40">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-30T13:04:04.515Z</v>
+        <v>2026-07-30T13:21:04.720Z</v>
       </c>
     </row>
     <row r="41">
@@ -1090,10 +1090,10 @@
         <v>Passed</v>
       </c>
       <c r="D41">
-        <v>1.67</v>
+        <v>0.98</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-30T13:04:05.515Z</v>
+        <v>2026-07-30T13:21:05.720Z</v>
       </c>
     </row>
     <row r="42">
@@ -1107,10 +1107,10 @@
         <v>Passed</v>
       </c>
       <c r="D42">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-30T13:04:06.515Z</v>
+        <v>2026-07-30T13:21:06.720Z</v>
       </c>
     </row>
     <row r="43">
@@ -1124,10 +1124,10 @@
         <v>Passed</v>
       </c>
       <c r="D43">
-        <v>1.15</v>
+        <v>0.74</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-30T13:04:07.515Z</v>
+        <v>2026-07-30T13:21:07.720Z</v>
       </c>
     </row>
     <row r="44">
@@ -1141,10 +1141,10 @@
         <v>Passed</v>
       </c>
       <c r="D44">
-        <v>0.76</v>
+        <v>1.01</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-30T13:04:08.515Z</v>
+        <v>2026-07-30T13:21:08.720Z</v>
       </c>
     </row>
     <row r="45">
@@ -1158,10 +1158,10 @@
         <v>Passed</v>
       </c>
       <c r="D45">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-30T13:04:09.515Z</v>
+        <v>2026-07-30T13:21:09.720Z</v>
       </c>
     </row>
     <row r="46">
@@ -1175,10 +1175,10 @@
         <v>Passed</v>
       </c>
       <c r="D46">
-        <v>1.68</v>
+        <v>0.77</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-30T13:04:10.515Z</v>
+        <v>2026-07-30T13:21:10.720Z</v>
       </c>
     </row>
     <row r="47">
@@ -1192,10 +1192,10 @@
         <v>Passed</v>
       </c>
       <c r="D47">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-30T13:04:11.515Z</v>
+        <v>2026-07-30T13:21:11.720Z</v>
       </c>
     </row>
     <row r="48">
@@ -1209,10 +1209,10 @@
         <v>Passed</v>
       </c>
       <c r="D48">
-        <v>1.44</v>
+        <v>0.87</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-30T13:04:12.515Z</v>
+        <v>2026-07-30T13:21:12.720Z</v>
       </c>
     </row>
     <row r="49">
@@ -1226,10 +1226,10 @@
         <v>Passed</v>
       </c>
       <c r="D49">
-        <v>1.53</v>
+        <v>0.91</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-30T13:04:13.515Z</v>
+        <v>2026-07-30T13:21:13.720Z</v>
       </c>
     </row>
     <row r="50">
@@ -1243,10 +1243,10 @@
         <v>Passed</v>
       </c>
       <c r="D50">
-        <v>0.54</v>
+        <v>1.38</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-30T13:04:14.515Z</v>
+        <v>2026-07-30T13:21:14.720Z</v>
       </c>
     </row>
     <row r="51">
@@ -1260,10 +1260,10 @@
         <v>Passed</v>
       </c>
       <c r="D51">
-        <v>0.27</v>
+        <v>1.99</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-30T13:04:15.515Z</v>
+        <v>2026-07-30T13:21:15.720Z</v>
       </c>
     </row>
     <row r="52">
@@ -1277,10 +1277,10 @@
         <v>Passed</v>
       </c>
       <c r="D52">
-        <v>0.97</v>
+        <v>1.93</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-30T13:04:16.515Z</v>
+        <v>2026-07-30T13:21:16.720Z</v>
       </c>
     </row>
     <row r="53">
@@ -1294,10 +1294,10 @@
         <v>Passed</v>
       </c>
       <c r="D53">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-30T13:04:17.515Z</v>
+        <v>2026-07-30T13:21:17.720Z</v>
       </c>
     </row>
     <row r="54">
@@ -1311,10 +1311,10 @@
         <v>Passed</v>
       </c>
       <c r="D54">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-30T13:04:18.515Z</v>
+        <v>2026-07-30T13:21:18.720Z</v>
       </c>
     </row>
     <row r="55">
@@ -1328,10 +1328,10 @@
         <v>Passed</v>
       </c>
       <c r="D55">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-30T13:04:19.515Z</v>
+        <v>2026-07-30T13:21:19.720Z</v>
       </c>
     </row>
     <row r="56">
@@ -1345,10 +1345,10 @@
         <v>Passed</v>
       </c>
       <c r="D56">
-        <v>1.89</v>
+        <v>0.87</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-30T13:04:20.515Z</v>
+        <v>2026-07-30T13:21:20.720Z</v>
       </c>
     </row>
     <row r="57">
@@ -1362,10 +1362,10 @@
         <v>Passed</v>
       </c>
       <c r="D57">
-        <v>1.23</v>
+        <v>1.97</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-30T13:04:21.515Z</v>
+        <v>2026-07-30T13:21:21.720Z</v>
       </c>
     </row>
     <row r="58">
@@ -1379,10 +1379,10 @@
         <v>Passed</v>
       </c>
       <c r="D58">
-        <v>1.37</v>
+        <v>0.14</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-30T13:04:22.515Z</v>
+        <v>2026-07-30T13:21:22.720Z</v>
       </c>
     </row>
     <row r="59">
@@ -1396,10 +1396,10 @@
         <v>Passed</v>
       </c>
       <c r="D59">
-        <v>0.56</v>
+        <v>1.21</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-30T13:04:23.515Z</v>
+        <v>2026-07-30T13:21:23.720Z</v>
       </c>
     </row>
     <row r="60">
@@ -1413,10 +1413,10 @@
         <v>Passed</v>
       </c>
       <c r="D60">
-        <v>1.87</v>
+        <v>1.16</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-30T13:04:24.515Z</v>
+        <v>2026-07-30T13:21:24.720Z</v>
       </c>
     </row>
     <row r="61">
@@ -1430,10 +1430,10 @@
         <v>Passed</v>
       </c>
       <c r="D61">
-        <v>0.23</v>
+        <v>0.71</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-30T13:04:25.515Z</v>
+        <v>2026-07-30T13:21:25.720Z</v>
       </c>
     </row>
     <row r="62">
@@ -1447,10 +1447,10 @@
         <v>Passed</v>
       </c>
       <c r="D62">
-        <v>1.82</v>
+        <v>0.15</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-30T13:04:26.515Z</v>
+        <v>2026-07-30T13:21:26.720Z</v>
       </c>
     </row>
     <row r="63">
@@ -1464,10 +1464,10 @@
         <v>Passed</v>
       </c>
       <c r="D63">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-30T13:04:27.515Z</v>
+        <v>2026-07-30T13:21:27.720Z</v>
       </c>
     </row>
     <row r="64">
@@ -1481,10 +1481,10 @@
         <v>Passed</v>
       </c>
       <c r="D64">
-        <v>1.98</v>
+        <v>0.53</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-30T13:04:28.515Z</v>
+        <v>2026-07-30T13:21:28.720Z</v>
       </c>
     </row>
     <row r="65">
@@ -1498,10 +1498,10 @@
         <v>Passed</v>
       </c>
       <c r="D65">
-        <v>0.78</v>
+        <v>1.33</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-30T13:04:29.515Z</v>
+        <v>2026-07-30T13:21:29.720Z</v>
       </c>
     </row>
     <row r="66">
@@ -1515,10 +1515,10 @@
         <v>Passed</v>
       </c>
       <c r="D66">
-        <v>0.05</v>
+        <v>0.53</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-30T13:04:30.515Z</v>
+        <v>2026-07-30T13:21:30.720Z</v>
       </c>
     </row>
     <row r="67">
@@ -1532,10 +1532,10 @@
         <v>Passed</v>
       </c>
       <c r="D67">
-        <v>1.56</v>
+        <v>0.33</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-30T13:04:31.515Z</v>
+        <v>2026-07-30T13:21:31.720Z</v>
       </c>
     </row>
     <row r="68">
@@ -1549,10 +1549,10 @@
         <v>Passed</v>
       </c>
       <c r="D68">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-30T13:04:32.515Z</v>
+        <v>2026-07-30T13:21:32.720Z</v>
       </c>
     </row>
     <row r="69">
@@ -1566,10 +1566,10 @@
         <v>Passed</v>
       </c>
       <c r="D69">
-        <v>1.55</v>
+        <v>0.75</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-30T13:04:33.515Z</v>
+        <v>2026-07-30T13:21:33.720Z</v>
       </c>
     </row>
     <row r="70">
@@ -1583,10 +1583,10 @@
         <v>Passed</v>
       </c>
       <c r="D70">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-30T13:04:34.515Z</v>
+        <v>2026-07-30T13:21:34.720Z</v>
       </c>
     </row>
     <row r="71">
@@ -1600,10 +1600,10 @@
         <v>Passed</v>
       </c>
       <c r="D71">
-        <v>1.51</v>
+        <v>1.99</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-30T13:04:35.515Z</v>
+        <v>2026-07-30T13:21:35.720Z</v>
       </c>
     </row>
     <row r="72">
@@ -1617,10 +1617,10 @@
         <v>Passed</v>
       </c>
       <c r="D72">
-        <v>0.96</v>
+        <v>1.85</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-30T13:04:36.515Z</v>
+        <v>2026-07-30T13:21:36.720Z</v>
       </c>
     </row>
     <row r="73">
@@ -1634,10 +1634,10 @@
         <v>Passed</v>
       </c>
       <c r="D73">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-30T13:04:37.515Z</v>
+        <v>2026-07-30T13:21:37.720Z</v>
       </c>
     </row>
     <row r="74">
@@ -1648,13 +1648,13 @@
         <v>Verify Security functionality module 73</v>
       </c>
       <c r="C74" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D74">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-30T13:04:38.515Z</v>
+        <v>2026-07-30T13:21:38.720Z</v>
       </c>
     </row>
     <row r="75">
@@ -1668,10 +1668,10 @@
         <v>Passed</v>
       </c>
       <c r="D75">
-        <v>1.01</v>
+        <v>0.43</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-30T13:04:39.515Z</v>
+        <v>2026-07-30T13:21:39.720Z</v>
       </c>
     </row>
     <row r="76">
@@ -1685,10 +1685,10 @@
         <v>Passed</v>
       </c>
       <c r="D76">
-        <v>0.1</v>
+        <v>0.67</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-30T13:04:40.515Z</v>
+        <v>2026-07-30T13:21:40.720Z</v>
       </c>
     </row>
     <row r="77">
@@ -1702,10 +1702,10 @@
         <v>Passed</v>
       </c>
       <c r="D77">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-30T13:04:41.515Z</v>
+        <v>2026-07-30T13:21:41.720Z</v>
       </c>
     </row>
     <row r="78">
@@ -1719,10 +1719,10 @@
         <v>Passed</v>
       </c>
       <c r="D78">
-        <v>0.82</v>
+        <v>1.13</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-30T13:04:42.515Z</v>
+        <v>2026-07-30T13:21:42.720Z</v>
       </c>
     </row>
     <row r="79">
@@ -1736,10 +1736,10 @@
         <v>Passed</v>
       </c>
       <c r="D79">
-        <v>0.52</v>
+        <v>1.49</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-30T13:04:43.515Z</v>
+        <v>2026-07-30T13:21:43.720Z</v>
       </c>
     </row>
     <row r="80">
@@ -1753,10 +1753,10 @@
         <v>Passed</v>
       </c>
       <c r="D80">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-30T13:04:44.515Z</v>
+        <v>2026-07-30T13:21:44.720Z</v>
       </c>
     </row>
     <row r="81">
@@ -1770,10 +1770,10 @@
         <v>Passed</v>
       </c>
       <c r="D81">
-        <v>0.69</v>
+        <v>1.35</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-30T13:04:45.515Z</v>
+        <v>2026-07-30T13:21:45.720Z</v>
       </c>
     </row>
     <row r="82">
@@ -1787,10 +1787,10 @@
         <v>Passed</v>
       </c>
       <c r="D82">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-30T13:04:46.515Z</v>
+        <v>2026-07-30T13:21:46.720Z</v>
       </c>
     </row>
     <row r="83">
@@ -1804,10 +1804,10 @@
         <v>Passed</v>
       </c>
       <c r="D83">
-        <v>0.34</v>
+        <v>1.27</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-30T13:04:47.515Z</v>
+        <v>2026-07-30T13:21:47.720Z</v>
       </c>
     </row>
     <row r="84">
@@ -1821,10 +1821,10 @@
         <v>Passed</v>
       </c>
       <c r="D84">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-30T13:04:48.515Z</v>
+        <v>2026-07-30T13:21:48.720Z</v>
       </c>
     </row>
     <row r="85">
@@ -1838,10 +1838,10 @@
         <v>Passed</v>
       </c>
       <c r="D85">
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-30T13:04:49.515Z</v>
+        <v>2026-07-30T13:21:49.720Z</v>
       </c>
     </row>
     <row r="86">
@@ -1855,10 +1855,10 @@
         <v>Passed</v>
       </c>
       <c r="D86">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-30T13:04:50.515Z</v>
+        <v>2026-07-30T13:21:50.720Z</v>
       </c>
     </row>
     <row r="87">
@@ -1872,10 +1872,10 @@
         <v>Passed</v>
       </c>
       <c r="D87">
-        <v>1.9</v>
+        <v>0.02</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-30T13:04:51.515Z</v>
+        <v>2026-07-30T13:21:51.720Z</v>
       </c>
     </row>
     <row r="88">
@@ -1889,10 +1889,10 @@
         <v>Passed</v>
       </c>
       <c r="D88">
-        <v>0.19</v>
+        <v>1.38</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-30T13:04:52.515Z</v>
+        <v>2026-07-30T13:21:52.720Z</v>
       </c>
     </row>
     <row r="89">
@@ -1906,10 +1906,10 @@
         <v>Passed</v>
       </c>
       <c r="D89">
-        <v>0.62</v>
+        <v>1.84</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-30T13:04:53.515Z</v>
+        <v>2026-07-30T13:21:53.720Z</v>
       </c>
     </row>
     <row r="90">
@@ -1923,10 +1923,10 @@
         <v>Passed</v>
       </c>
       <c r="D90">
-        <v>1.49</v>
+        <v>0.94</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-30T13:04:54.515Z</v>
+        <v>2026-07-30T13:21:54.720Z</v>
       </c>
     </row>
     <row r="91">
@@ -1940,10 +1940,10 @@
         <v>Passed</v>
       </c>
       <c r="D91">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-30T13:04:55.515Z</v>
+        <v>2026-07-30T13:21:55.720Z</v>
       </c>
     </row>
     <row r="92">
@@ -1957,10 +1957,10 @@
         <v>Passed</v>
       </c>
       <c r="D92">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-30T13:04:56.515Z</v>
+        <v>2026-07-30T13:21:56.720Z</v>
       </c>
     </row>
     <row r="93">
@@ -1974,10 +1974,10 @@
         <v>Passed</v>
       </c>
       <c r="D93">
-        <v>0.9</v>
+        <v>1.96</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-30T13:04:57.515Z</v>
+        <v>2026-07-30T13:21:57.720Z</v>
       </c>
     </row>
     <row r="94">
@@ -1991,10 +1991,10 @@
         <v>Passed</v>
       </c>
       <c r="D94">
-        <v>1.84</v>
+        <v>0.07</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-30T13:04:58.515Z</v>
+        <v>2026-07-30T13:21:58.720Z</v>
       </c>
     </row>
     <row r="95">
@@ -2008,10 +2008,10 @@
         <v>Passed</v>
       </c>
       <c r="D95">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-30T13:04:59.515Z</v>
+        <v>2026-07-30T13:21:59.720Z</v>
       </c>
     </row>
     <row r="96">
@@ -2025,10 +2025,10 @@
         <v>Passed</v>
       </c>
       <c r="D96">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-30T13:05:00.515Z</v>
+        <v>2026-07-30T13:22:00.720Z</v>
       </c>
     </row>
     <row r="97">
@@ -2042,10 +2042,10 @@
         <v>Passed</v>
       </c>
       <c r="D97">
-        <v>0.69</v>
+        <v>1.61</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-30T13:05:01.515Z</v>
+        <v>2026-07-30T13:22:01.720Z</v>
       </c>
     </row>
     <row r="98">
@@ -2059,10 +2059,10 @@
         <v>Passed</v>
       </c>
       <c r="D98">
-        <v>0.25</v>
+        <v>1.7</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-30T13:05:02.515Z</v>
+        <v>2026-07-30T13:22:02.720Z</v>
       </c>
     </row>
     <row r="99">
@@ -2076,10 +2076,10 @@
         <v>Passed</v>
       </c>
       <c r="D99">
-        <v>1.35</v>
+        <v>0.53</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-30T13:05:03.515Z</v>
+        <v>2026-07-30T13:22:03.720Z</v>
       </c>
     </row>
     <row r="100">
@@ -2093,10 +2093,10 @@
         <v>Passed</v>
       </c>
       <c r="D100">
-        <v>0.53</v>
+        <v>1.52</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-30T13:05:04.515Z</v>
+        <v>2026-07-30T13:22:04.720Z</v>
       </c>
     </row>
     <row r="101">
@@ -2110,10 +2110,10 @@
         <v>Passed</v>
       </c>
       <c r="D101">
-        <v>1.06</v>
+        <v>0.84</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-30T13:05:05.515Z</v>
+        <v>2026-07-30T13:22:05.720Z</v>
       </c>
     </row>
     <row r="102">
@@ -2127,10 +2127,10 @@
         <v>Passed</v>
       </c>
       <c r="D102">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-30T13:05:06.515Z</v>
+        <v>2026-07-30T13:22:06.720Z</v>
       </c>
     </row>
     <row r="103">
@@ -2144,10 +2144,10 @@
         <v>Passed</v>
       </c>
       <c r="D103">
-        <v>0.01</v>
+        <v>0.26</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-30T13:05:07.515Z</v>
+        <v>2026-07-30T13:22:07.720Z</v>
       </c>
     </row>
     <row r="104">
@@ -2161,10 +2161,10 @@
         <v>Passed</v>
       </c>
       <c r="D104">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-30T13:05:08.515Z</v>
+        <v>2026-07-30T13:22:08.720Z</v>
       </c>
     </row>
     <row r="105">
@@ -2178,10 +2178,10 @@
         <v>Passed</v>
       </c>
       <c r="D105">
-        <v>0.56</v>
+        <v>1.23</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-30T13:05:09.515Z</v>
+        <v>2026-07-30T13:22:09.720Z</v>
       </c>
     </row>
     <row r="106">
@@ -2195,10 +2195,10 @@
         <v>Passed</v>
       </c>
       <c r="D106">
-        <v>0.14</v>
+        <v>1.39</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-30T13:05:10.515Z</v>
+        <v>2026-07-30T13:22:10.720Z</v>
       </c>
     </row>
     <row r="107">
@@ -2212,10 +2212,10 @@
         <v>Passed</v>
       </c>
       <c r="D107">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-30T13:05:11.515Z</v>
+        <v>2026-07-30T13:22:11.720Z</v>
       </c>
     </row>
     <row r="108">
@@ -2229,10 +2229,10 @@
         <v>Passed</v>
       </c>
       <c r="D108">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-30T13:05:12.515Z</v>
+        <v>2026-07-30T13:22:12.720Z</v>
       </c>
     </row>
     <row r="109">
@@ -2246,10 +2246,10 @@
         <v>Passed</v>
       </c>
       <c r="D109">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-30T13:05:13.515Z</v>
+        <v>2026-07-30T13:22:13.720Z</v>
       </c>
     </row>
     <row r="110">
@@ -2263,10 +2263,10 @@
         <v>Passed</v>
       </c>
       <c r="D110">
-        <v>1.8</v>
+        <v>0.67</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-30T13:05:14.515Z</v>
+        <v>2026-07-30T13:22:14.720Z</v>
       </c>
     </row>
     <row r="111">
@@ -2280,10 +2280,10 @@
         <v>Passed</v>
       </c>
       <c r="D111">
-        <v>0.36</v>
+        <v>0.07</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-30T13:05:15.515Z</v>
+        <v>2026-07-30T13:22:15.720Z</v>
       </c>
     </row>
     <row r="112">
@@ -2297,10 +2297,10 @@
         <v>Passed</v>
       </c>
       <c r="D112">
-        <v>0.39</v>
+        <v>0.79</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-30T13:05:16.515Z</v>
+        <v>2026-07-30T13:22:16.720Z</v>
       </c>
     </row>
     <row r="113">
@@ -2317,7 +2317,7 @@
         <v>1.49</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-30T13:05:17.515Z</v>
+        <v>2026-07-30T13:22:17.720Z</v>
       </c>
     </row>
     <row r="114">
@@ -2331,10 +2331,10 @@
         <v>Passed</v>
       </c>
       <c r="D114">
-        <v>1.36</v>
+        <v>0.68</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-30T13:05:18.515Z</v>
+        <v>2026-07-30T13:22:18.720Z</v>
       </c>
     </row>
     <row r="115">
@@ -2348,10 +2348,10 @@
         <v>Passed</v>
       </c>
       <c r="D115">
-        <v>0.35</v>
+        <v>1.11</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-30T13:05:19.515Z</v>
+        <v>2026-07-30T13:22:19.720Z</v>
       </c>
     </row>
     <row r="116">
@@ -2362,13 +2362,13 @@
         <v>Verify Security functionality module 115</v>
       </c>
       <c r="C116" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D116">
-        <v>1.76</v>
+        <v>1.05</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-30T13:05:20.515Z</v>
+        <v>2026-07-30T13:22:20.720Z</v>
       </c>
     </row>
     <row r="117">
@@ -2382,10 +2382,10 @@
         <v>Passed</v>
       </c>
       <c r="D117">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-30T13:05:21.515Z</v>
+        <v>2026-07-30T13:22:21.720Z</v>
       </c>
     </row>
     <row r="118">
@@ -2399,10 +2399,10 @@
         <v>Passed</v>
       </c>
       <c r="D118">
-        <v>1.86</v>
+        <v>0.94</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-30T13:05:22.515Z</v>
+        <v>2026-07-30T13:22:22.720Z</v>
       </c>
     </row>
     <row r="119">
@@ -2416,10 +2416,10 @@
         <v>Passed</v>
       </c>
       <c r="D119">
-        <v>1.45</v>
+        <v>0.32</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-30T13:05:23.515Z</v>
+        <v>2026-07-30T13:22:23.720Z</v>
       </c>
     </row>
     <row r="120">
@@ -2433,10 +2433,10 @@
         <v>Passed</v>
       </c>
       <c r="D120">
-        <v>1.49</v>
+        <v>0.95</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-30T13:05:24.515Z</v>
+        <v>2026-07-30T13:22:24.720Z</v>
       </c>
     </row>
     <row r="121">
@@ -2450,10 +2450,10 @@
         <v>Passed</v>
       </c>
       <c r="D121">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-30T13:05:25.515Z</v>
+        <v>2026-07-30T13:22:25.720Z</v>
       </c>
     </row>
     <row r="122">
@@ -2467,10 +2467,10 @@
         <v>Passed</v>
       </c>
       <c r="D122">
-        <v>1.36</v>
+        <v>0.9</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-30T13:05:26.515Z</v>
+        <v>2026-07-30T13:22:26.720Z</v>
       </c>
     </row>
     <row r="123">
@@ -2481,13 +2481,13 @@
         <v>Verify Security functionality module 122</v>
       </c>
       <c r="C123" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D123">
-        <v>1.82</v>
+        <v>0.88</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-30T13:05:27.515Z</v>
+        <v>2026-07-30T13:22:27.720Z</v>
       </c>
     </row>
     <row r="124">
@@ -2501,10 +2501,10 @@
         <v>Passed</v>
       </c>
       <c r="D124">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-30T13:05:28.515Z</v>
+        <v>2026-07-30T13:22:28.720Z</v>
       </c>
     </row>
     <row r="125">
@@ -2518,10 +2518,10 @@
         <v>Passed</v>
       </c>
       <c r="D125">
-        <v>1.61</v>
+        <v>0.97</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-30T13:05:29.515Z</v>
+        <v>2026-07-30T13:22:29.720Z</v>
       </c>
     </row>
     <row r="126">
@@ -2535,10 +2535,10 @@
         <v>Passed</v>
       </c>
       <c r="D126">
-        <v>0.6</v>
+        <v>1.31</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-30T13:05:30.515Z</v>
+        <v>2026-07-30T13:22:30.720Z</v>
       </c>
     </row>
     <row r="127">
@@ -2552,10 +2552,10 @@
         <v>Passed</v>
       </c>
       <c r="D127">
-        <v>0.4</v>
+        <v>1.78</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-30T13:05:31.515Z</v>
+        <v>2026-07-30T13:22:31.720Z</v>
       </c>
     </row>
     <row r="128">
@@ -2569,10 +2569,10 @@
         <v>Passed</v>
       </c>
       <c r="D128">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-30T13:05:32.515Z</v>
+        <v>2026-07-30T13:22:32.720Z</v>
       </c>
     </row>
     <row r="129">
@@ -2586,10 +2586,10 @@
         <v>Passed</v>
       </c>
       <c r="D129">
-        <v>0.82</v>
+        <v>1.22</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-30T13:05:33.515Z</v>
+        <v>2026-07-30T13:22:33.720Z</v>
       </c>
     </row>
     <row r="130">
@@ -2603,10 +2603,10 @@
         <v>Passed</v>
       </c>
       <c r="D130">
-        <v>1.67</v>
+        <v>0.59</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-30T13:05:34.515Z</v>
+        <v>2026-07-30T13:22:34.720Z</v>
       </c>
     </row>
     <row r="131">
@@ -2620,10 +2620,10 @@
         <v>Passed</v>
       </c>
       <c r="D131">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-30T13:05:35.515Z</v>
+        <v>2026-07-30T13:22:35.720Z</v>
       </c>
     </row>
     <row r="132">
@@ -2637,10 +2637,10 @@
         <v>Passed</v>
       </c>
       <c r="D132">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-30T13:05:36.515Z</v>
+        <v>2026-07-30T13:22:36.720Z</v>
       </c>
     </row>
     <row r="133">
@@ -2654,10 +2654,10 @@
         <v>Passed</v>
       </c>
       <c r="D133">
-        <v>0.79</v>
+        <v>1.13</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-30T13:05:37.515Z</v>
+        <v>2026-07-30T13:22:37.720Z</v>
       </c>
     </row>
     <row r="134">
@@ -2671,10 +2671,10 @@
         <v>Passed</v>
       </c>
       <c r="D134">
-        <v>0.05</v>
+        <v>1.73</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-30T13:05:38.515Z</v>
+        <v>2026-07-30T13:22:38.720Z</v>
       </c>
     </row>
     <row r="135">
@@ -2688,10 +2688,10 @@
         <v>Passed</v>
       </c>
       <c r="D135">
-        <v>1.11</v>
+        <v>0.44</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-30T13:05:39.515Z</v>
+        <v>2026-07-30T13:22:39.720Z</v>
       </c>
     </row>
     <row r="136">
@@ -2705,10 +2705,10 @@
         <v>Passed</v>
       </c>
       <c r="D136">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-30T13:05:40.515Z</v>
+        <v>2026-07-30T13:22:40.720Z</v>
       </c>
     </row>
     <row r="137">
@@ -2722,10 +2722,10 @@
         <v>Passed</v>
       </c>
       <c r="D137">
-        <v>1.43</v>
+        <v>1</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-30T13:05:41.515Z</v>
+        <v>2026-07-30T13:22:41.720Z</v>
       </c>
     </row>
     <row r="138">
@@ -2739,10 +2739,10 @@
         <v>Passed</v>
       </c>
       <c r="D138">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-30T13:05:42.515Z</v>
+        <v>2026-07-30T13:22:42.720Z</v>
       </c>
     </row>
     <row r="139">
@@ -2756,10 +2756,10 @@
         <v>Passed</v>
       </c>
       <c r="D139">
-        <v>1.73</v>
+        <v>0.81</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-30T13:05:43.515Z</v>
+        <v>2026-07-30T13:22:43.720Z</v>
       </c>
     </row>
     <row r="140">
@@ -2773,10 +2773,10 @@
         <v>Passed</v>
       </c>
       <c r="D140">
-        <v>1.73</v>
+        <v>1.12</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-30T13:05:44.515Z</v>
+        <v>2026-07-30T13:22:44.720Z</v>
       </c>
     </row>
     <row r="141">
@@ -2790,10 +2790,10 @@
         <v>Passed</v>
       </c>
       <c r="D141">
-        <v>1.03</v>
+        <v>0.42</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-30T13:05:45.515Z</v>
+        <v>2026-07-30T13:22:45.720Z</v>
       </c>
     </row>
     <row r="142">
@@ -2807,10 +2807,10 @@
         <v>Passed</v>
       </c>
       <c r="D142">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-30T13:05:46.515Z</v>
+        <v>2026-07-30T13:22:46.720Z</v>
       </c>
     </row>
     <row r="143">
@@ -2824,10 +2824,10 @@
         <v>Passed</v>
       </c>
       <c r="D143">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-30T13:05:47.515Z</v>
+        <v>2026-07-30T13:22:47.720Z</v>
       </c>
     </row>
     <row r="144">
@@ -2841,10 +2841,10 @@
         <v>Passed</v>
       </c>
       <c r="D144">
-        <v>1.08</v>
+        <v>1.93</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-30T13:05:48.515Z</v>
+        <v>2026-07-30T13:22:48.720Z</v>
       </c>
     </row>
     <row r="145">
@@ -2858,10 +2858,10 @@
         <v>Passed</v>
       </c>
       <c r="D145">
-        <v>0.12</v>
+        <v>0.69</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-30T13:05:49.515Z</v>
+        <v>2026-07-30T13:22:49.720Z</v>
       </c>
     </row>
     <row r="146">
@@ -2875,10 +2875,10 @@
         <v>Passed</v>
       </c>
       <c r="D146">
-        <v>0.2</v>
+        <v>0.86</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-30T13:05:50.515Z</v>
+        <v>2026-07-30T13:22:50.720Z</v>
       </c>
     </row>
     <row r="147">
@@ -2892,10 +2892,10 @@
         <v>Passed</v>
       </c>
       <c r="D147">
-        <v>0.89</v>
+        <v>1.28</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-30T13:05:51.515Z</v>
+        <v>2026-07-30T13:22:51.720Z</v>
       </c>
     </row>
     <row r="148">
@@ -2909,10 +2909,10 @@
         <v>Passed</v>
       </c>
       <c r="D148">
-        <v>1.07</v>
+        <v>1.92</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-30T13:05:52.515Z</v>
+        <v>2026-07-30T13:22:52.720Z</v>
       </c>
     </row>
     <row r="149">
@@ -2926,10 +2926,10 @@
         <v>Passed</v>
       </c>
       <c r="D149">
-        <v>1.36</v>
+        <v>0.27</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-30T13:05:53.515Z</v>
+        <v>2026-07-30T13:22:53.720Z</v>
       </c>
     </row>
     <row r="150">
@@ -2943,10 +2943,10 @@
         <v>Passed</v>
       </c>
       <c r="D150">
-        <v>0.42</v>
+        <v>0.07</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-30T13:05:54.515Z</v>
+        <v>2026-07-30T13:22:54.720Z</v>
       </c>
     </row>
     <row r="151">
@@ -2960,10 +2960,10 @@
         <v>Passed</v>
       </c>
       <c r="D151">
-        <v>1.83</v>
+        <v>0.02</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-30T13:05:55.515Z</v>
+        <v>2026-07-30T13:22:55.720Z</v>
       </c>
     </row>
     <row r="152">
@@ -2977,10 +2977,10 @@
         <v>Passed</v>
       </c>
       <c r="D152">
-        <v>1.89</v>
+        <v>0.47</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-30T13:05:56.515Z</v>
+        <v>2026-07-30T13:22:56.720Z</v>
       </c>
     </row>
     <row r="153">
@@ -2994,10 +2994,10 @@
         <v>Passed</v>
       </c>
       <c r="D153">
-        <v>1.39</v>
+        <v>0.49</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-30T13:05:57.515Z</v>
+        <v>2026-07-30T13:22:57.720Z</v>
       </c>
     </row>
     <row r="154">
@@ -3011,10 +3011,10 @@
         <v>Passed</v>
       </c>
       <c r="D154">
-        <v>1.39</v>
+        <v>0.78</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-30T13:05:58.515Z</v>
+        <v>2026-07-30T13:22:58.720Z</v>
       </c>
     </row>
     <row r="155">
@@ -3028,10 +3028,10 @@
         <v>Passed</v>
       </c>
       <c r="D155">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-30T13:05:59.515Z</v>
+        <v>2026-07-30T13:22:59.720Z</v>
       </c>
     </row>
     <row r="156">
@@ -3045,10 +3045,10 @@
         <v>Passed</v>
       </c>
       <c r="D156">
-        <v>1.08</v>
+        <v>1.63</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-30T13:06:00.515Z</v>
+        <v>2026-07-30T13:23:00.720Z</v>
       </c>
     </row>
     <row r="157">
@@ -3062,10 +3062,10 @@
         <v>Passed</v>
       </c>
       <c r="D157">
-        <v>0.48</v>
+        <v>1.02</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-30T13:06:01.515Z</v>
+        <v>2026-07-30T13:23:01.720Z</v>
       </c>
     </row>
     <row r="158">
@@ -3079,10 +3079,10 @@
         <v>Passed</v>
       </c>
       <c r="D158">
-        <v>1.34</v>
+        <v>0.64</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-30T13:06:02.515Z</v>
+        <v>2026-07-30T13:23:02.720Z</v>
       </c>
     </row>
     <row r="159">
@@ -3096,10 +3096,10 @@
         <v>Passed</v>
       </c>
       <c r="D159">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-30T13:06:03.515Z</v>
+        <v>2026-07-30T13:23:03.720Z</v>
       </c>
     </row>
     <row r="160">
@@ -3113,10 +3113,10 @@
         <v>Passed</v>
       </c>
       <c r="D160">
-        <v>0.4</v>
+        <v>1.67</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-30T13:06:04.515Z</v>
+        <v>2026-07-30T13:23:04.720Z</v>
       </c>
     </row>
     <row r="161">
@@ -3130,10 +3130,10 @@
         <v>Passed</v>
       </c>
       <c r="D161">
-        <v>1.28</v>
+        <v>1.96</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-30T13:06:05.515Z</v>
+        <v>2026-07-30T13:23:05.720Z</v>
       </c>
     </row>
     <row r="162">
@@ -3147,10 +3147,10 @@
         <v>Passed</v>
       </c>
       <c r="D162">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-30T13:06:06.515Z</v>
+        <v>2026-07-30T13:23:06.720Z</v>
       </c>
     </row>
     <row r="163">
@@ -3164,10 +3164,10 @@
         <v>Passed</v>
       </c>
       <c r="D163">
-        <v>0.28</v>
+        <v>1.3</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-30T13:06:07.515Z</v>
+        <v>2026-07-30T13:23:07.720Z</v>
       </c>
     </row>
     <row r="164">
@@ -3181,10 +3181,10 @@
         <v>Passed</v>
       </c>
       <c r="D164">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-30T13:06:08.515Z</v>
+        <v>2026-07-30T13:23:08.720Z</v>
       </c>
     </row>
     <row r="165">
@@ -3198,10 +3198,10 @@
         <v>Passed</v>
       </c>
       <c r="D165">
-        <v>0.31</v>
+        <v>0.95</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-30T13:06:09.515Z</v>
+        <v>2026-07-30T13:23:09.720Z</v>
       </c>
     </row>
     <row r="166">
@@ -3215,10 +3215,10 @@
         <v>Passed</v>
       </c>
       <c r="D166">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-30T13:06:10.515Z</v>
+        <v>2026-07-30T13:23:10.720Z</v>
       </c>
     </row>
     <row r="167">
@@ -3232,10 +3232,10 @@
         <v>Passed</v>
       </c>
       <c r="D167">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-30T13:06:11.515Z</v>
+        <v>2026-07-30T13:23:11.720Z</v>
       </c>
     </row>
     <row r="168">
@@ -3249,10 +3249,10 @@
         <v>Passed</v>
       </c>
       <c r="D168">
-        <v>1.12</v>
+        <v>0.16</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-30T13:06:12.515Z</v>
+        <v>2026-07-30T13:23:12.720Z</v>
       </c>
     </row>
     <row r="169">
@@ -3266,10 +3266,10 @@
         <v>Passed</v>
       </c>
       <c r="D169">
-        <v>0.33</v>
+        <v>1.68</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-30T13:06:13.515Z</v>
+        <v>2026-07-30T13:23:13.720Z</v>
       </c>
     </row>
     <row r="170">
@@ -3283,10 +3283,10 @@
         <v>Passed</v>
       </c>
       <c r="D170">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-30T13:06:14.515Z</v>
+        <v>2026-07-30T13:23:14.720Z</v>
       </c>
     </row>
     <row r="171">
@@ -3300,10 +3300,10 @@
         <v>Passed</v>
       </c>
       <c r="D171">
-        <v>0.3</v>
+        <v>0.87</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-30T13:06:15.515Z</v>
+        <v>2026-07-30T13:23:15.720Z</v>
       </c>
     </row>
     <row r="172">
@@ -3317,10 +3317,10 @@
         <v>Passed</v>
       </c>
       <c r="D172">
-        <v>0.41</v>
+        <v>1.9</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-30T13:06:16.515Z</v>
+        <v>2026-07-30T13:23:16.720Z</v>
       </c>
     </row>
     <row r="173">
@@ -3337,7 +3337,7 @@
         <v>1.64</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-30T13:06:17.515Z</v>
+        <v>2026-07-30T13:23:17.720Z</v>
       </c>
     </row>
     <row r="174">
@@ -3351,10 +3351,10 @@
         <v>Passed</v>
       </c>
       <c r="D174">
-        <v>0.12</v>
+        <v>1.49</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-30T13:06:18.515Z</v>
+        <v>2026-07-30T13:23:18.720Z</v>
       </c>
     </row>
     <row r="175">
@@ -3368,10 +3368,10 @@
         <v>Passed</v>
       </c>
       <c r="D175">
-        <v>0.07</v>
+        <v>0.62</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-30T13:06:19.515Z</v>
+        <v>2026-07-30T13:23:19.720Z</v>
       </c>
     </row>
     <row r="176">
@@ -3385,10 +3385,10 @@
         <v>Passed</v>
       </c>
       <c r="D176">
-        <v>0.78</v>
+        <v>0.29</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-30T13:06:20.515Z</v>
+        <v>2026-07-30T13:23:20.720Z</v>
       </c>
     </row>
     <row r="177">
@@ -3402,10 +3402,10 @@
         <v>Passed</v>
       </c>
       <c r="D177">
-        <v>0.18</v>
+        <v>1.83</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-30T13:06:21.515Z</v>
+        <v>2026-07-30T13:23:21.720Z</v>
       </c>
     </row>
     <row r="178">
@@ -3419,10 +3419,10 @@
         <v>Passed</v>
       </c>
       <c r="D178">
-        <v>0.64</v>
+        <v>0.88</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-30T13:06:22.515Z</v>
+        <v>2026-07-30T13:23:22.720Z</v>
       </c>
     </row>
     <row r="179">
@@ -3436,10 +3436,10 @@
         <v>Passed</v>
       </c>
       <c r="D179">
-        <v>1.32</v>
+        <v>0.26</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-30T13:06:23.515Z</v>
+        <v>2026-07-30T13:23:23.720Z</v>
       </c>
     </row>
     <row r="180">
@@ -3450,13 +3450,13 @@
         <v>Verify Security functionality module 179</v>
       </c>
       <c r="C180" t="str">
-        <v>Passed</v>
+        <v>Failed</v>
       </c>
       <c r="D180">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-30T13:06:24.515Z</v>
+        <v>2026-07-30T13:23:24.720Z</v>
       </c>
     </row>
     <row r="181">
@@ -3470,10 +3470,10 @@
         <v>Passed</v>
       </c>
       <c r="D181">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-30T13:06:25.515Z</v>
+        <v>2026-07-30T13:23:25.720Z</v>
       </c>
     </row>
     <row r="182">
@@ -3487,10 +3487,10 @@
         <v>Passed</v>
       </c>
       <c r="D182">
-        <v>1.85</v>
+        <v>0.53</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-30T13:06:26.515Z</v>
+        <v>2026-07-30T13:23:26.720Z</v>
       </c>
     </row>
     <row r="183">
@@ -3504,10 +3504,10 @@
         <v>Passed</v>
       </c>
       <c r="D183">
-        <v>0.25</v>
+        <v>1.71</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-30T13:06:27.515Z</v>
+        <v>2026-07-30T13:23:27.720Z</v>
       </c>
     </row>
     <row r="184">
@@ -3521,10 +3521,10 @@
         <v>Passed</v>
       </c>
       <c r="D184">
-        <v>0.88</v>
+        <v>1.09</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-30T13:06:28.515Z</v>
+        <v>2026-07-30T13:23:28.720Z</v>
       </c>
     </row>
     <row r="185">
@@ -3538,10 +3538,10 @@
         <v>Passed</v>
       </c>
       <c r="D185">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-30T13:06:29.515Z</v>
+        <v>2026-07-30T13:23:29.720Z</v>
       </c>
     </row>
     <row r="186">
@@ -3555,10 +3555,10 @@
         <v>Passed</v>
       </c>
       <c r="D186">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-30T13:06:30.515Z</v>
+        <v>2026-07-30T13:23:30.720Z</v>
       </c>
     </row>
     <row r="187">
@@ -3572,10 +3572,10 @@
         <v>Passed</v>
       </c>
       <c r="D187">
-        <v>1.39</v>
+        <v>0.73</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-30T13:06:31.515Z</v>
+        <v>2026-07-30T13:23:31.720Z</v>
       </c>
     </row>
     <row r="188">
@@ -3589,10 +3589,10 @@
         <v>Passed</v>
       </c>
       <c r="D188">
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-30T13:06:32.515Z</v>
+        <v>2026-07-30T13:23:32.720Z</v>
       </c>
     </row>
     <row r="189">
@@ -3606,10 +3606,10 @@
         <v>Passed</v>
       </c>
       <c r="D189">
-        <v>0.18</v>
+        <v>1.32</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-30T13:06:33.515Z</v>
+        <v>2026-07-30T13:23:33.720Z</v>
       </c>
     </row>
     <row r="190">
@@ -3623,10 +3623,10 @@
         <v>Passed</v>
       </c>
       <c r="D190">
-        <v>0.54</v>
+        <v>0.69</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-30T13:06:34.515Z</v>
+        <v>2026-07-30T13:23:34.720Z</v>
       </c>
     </row>
     <row r="191">
@@ -3640,10 +3640,10 @@
         <v>Passed</v>
       </c>
       <c r="D191">
-        <v>0.25</v>
+        <v>0.87</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-30T13:06:35.515Z</v>
+        <v>2026-07-30T13:23:35.720Z</v>
       </c>
     </row>
     <row r="192">
@@ -3657,10 +3657,10 @@
         <v>Passed</v>
       </c>
       <c r="D192">
-        <v>0.04</v>
+        <v>1.68</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-30T13:06:36.515Z</v>
+        <v>2026-07-30T13:23:36.720Z</v>
       </c>
     </row>
     <row r="193">
@@ -3674,10 +3674,10 @@
         <v>Passed</v>
       </c>
       <c r="D193">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-30T13:06:37.515Z</v>
+        <v>2026-07-30T13:23:37.720Z</v>
       </c>
     </row>
     <row r="194">
@@ -3691,10 +3691,10 @@
         <v>Passed</v>
       </c>
       <c r="D194">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-30T13:06:38.515Z</v>
+        <v>2026-07-30T13:23:38.720Z</v>
       </c>
     </row>
     <row r="195">
@@ -3708,10 +3708,10 @@
         <v>Passed</v>
       </c>
       <c r="D195">
-        <v>0.78</v>
+        <v>1.04</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-30T13:06:39.515Z</v>
+        <v>2026-07-30T13:23:39.720Z</v>
       </c>
     </row>
     <row r="196">
@@ -3725,10 +3725,10 @@
         <v>Passed</v>
       </c>
       <c r="D196">
-        <v>0.44</v>
+        <v>0.69</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-30T13:06:40.515Z</v>
+        <v>2026-07-30T13:23:40.720Z</v>
       </c>
     </row>
     <row r="197">
@@ -3742,10 +3742,10 @@
         <v>Passed</v>
       </c>
       <c r="D197">
-        <v>1.13</v>
+        <v>1.68</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-30T13:06:41.515Z</v>
+        <v>2026-07-30T13:23:41.720Z</v>
       </c>
     </row>
     <row r="198">
@@ -3759,10 +3759,10 @@
         <v>Passed</v>
       </c>
       <c r="D198">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-30T13:06:42.515Z</v>
+        <v>2026-07-30T13:23:42.720Z</v>
       </c>
     </row>
     <row r="199">
@@ -3776,10 +3776,10 @@
         <v>Passed</v>
       </c>
       <c r="D199">
-        <v>0.23</v>
+        <v>1.32</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-30T13:06:43.515Z</v>
+        <v>2026-07-30T13:23:43.720Z</v>
       </c>
     </row>
     <row r="200">
@@ -3793,10 +3793,10 @@
         <v>Passed</v>
       </c>
       <c r="D200">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-30T13:06:44.515Z</v>
+        <v>2026-07-30T13:23:44.720Z</v>
       </c>
     </row>
     <row r="201">
@@ -3810,10 +3810,10 @@
         <v>Passed</v>
       </c>
       <c r="D201">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-30T13:06:45.515Z</v>
+        <v>2026-07-30T13:23:45.720Z</v>
       </c>
     </row>
     <row r="202">
@@ -3827,10 +3827,10 @@
         <v>Passed</v>
       </c>
       <c r="D202">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-30T13:06:46.515Z</v>
+        <v>2026-07-30T13:23:46.720Z</v>
       </c>
     </row>
     <row r="203">
@@ -3844,10 +3844,10 @@
         <v>Passed</v>
       </c>
       <c r="D203">
-        <v>1.51</v>
+        <v>0.35</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-30T13:06:47.515Z</v>
+        <v>2026-07-30T13:23:47.720Z</v>
       </c>
     </row>
     <row r="204">
@@ -3861,10 +3861,10 @@
         <v>Passed</v>
       </c>
       <c r="D204">
-        <v>0.13</v>
+        <v>0.86</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-30T13:06:48.515Z</v>
+        <v>2026-07-30T13:23:48.720Z</v>
       </c>
     </row>
     <row r="205">
@@ -3878,10 +3878,10 @@
         <v>Passed</v>
       </c>
       <c r="D205">
-        <v>1.83</v>
+        <v>0.86</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-30T13:06:49.515Z</v>
+        <v>2026-07-30T13:23:49.720Z</v>
       </c>
     </row>
     <row r="206">
@@ -3895,10 +3895,10 @@
         <v>Passed</v>
       </c>
       <c r="D206">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-30T13:06:50.515Z</v>
+        <v>2026-07-30T13:23:50.720Z</v>
       </c>
     </row>
     <row r="207">
@@ -3912,10 +3912,10 @@
         <v>Passed</v>
       </c>
       <c r="D207">
-        <v>0.14</v>
+        <v>0.03</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-30T13:06:51.515Z</v>
+        <v>2026-07-30T13:23:51.720Z</v>
       </c>
     </row>
     <row r="208">
@@ -3929,10 +3929,10 @@
         <v>Passed</v>
       </c>
       <c r="D208">
-        <v>0.41</v>
+        <v>0.81</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-30T13:06:52.515Z</v>
+        <v>2026-07-30T13:23:52.720Z</v>
       </c>
     </row>
     <row r="209">
@@ -3946,10 +3946,10 @@
         <v>Passed</v>
       </c>
       <c r="D209">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-30T13:06:53.515Z</v>
+        <v>2026-07-30T13:23:53.720Z</v>
       </c>
     </row>
     <row r="210">
@@ -3963,10 +3963,10 @@
         <v>Passed</v>
       </c>
       <c r="D210">
-        <v>0.09</v>
+        <v>1.78</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-30T13:06:54.515Z</v>
+        <v>2026-07-30T13:23:54.720Z</v>
       </c>
     </row>
     <row r="211">
@@ -3980,10 +3980,10 @@
         <v>Passed</v>
       </c>
       <c r="D211">
-        <v>0.74</v>
+        <v>0.07</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-30T13:06:55.515Z</v>
+        <v>2026-07-30T13:23:55.720Z</v>
       </c>
     </row>
     <row r="212">
@@ -3997,10 +3997,10 @@
         <v>Passed</v>
       </c>
       <c r="D212">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-30T13:06:56.515Z</v>
+        <v>2026-07-30T13:23:56.720Z</v>
       </c>
     </row>
     <row r="213">
@@ -4014,10 +4014,10 @@
         <v>Passed</v>
       </c>
       <c r="D213">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-30T13:06:57.515Z</v>
+        <v>2026-07-30T13:23:57.720Z</v>
       </c>
     </row>
     <row r="214">
@@ -4031,10 +4031,10 @@
         <v>Passed</v>
       </c>
       <c r="D214">
-        <v>0.49</v>
+        <v>1.24</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-30T13:06:58.515Z</v>
+        <v>2026-07-30T13:23:58.720Z</v>
       </c>
     </row>
     <row r="215">
@@ -4048,10 +4048,10 @@
         <v>Passed</v>
       </c>
       <c r="D215">
-        <v>1.14</v>
+        <v>1.96</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-30T13:06:59.515Z</v>
+        <v>2026-07-30T13:23:59.720Z</v>
       </c>
     </row>
     <row r="216">
@@ -4065,10 +4065,10 @@
         <v>Passed</v>
       </c>
       <c r="D216">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-30T13:07:00.515Z</v>
+        <v>2026-07-30T13:24:00.720Z</v>
       </c>
     </row>
     <row r="217">
@@ -4082,10 +4082,10 @@
         <v>Passed</v>
       </c>
       <c r="D217">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-30T13:07:01.515Z</v>
+        <v>2026-07-30T13:24:01.720Z</v>
       </c>
     </row>
     <row r="218">
@@ -4099,10 +4099,10 @@
         <v>Passed</v>
       </c>
       <c r="D218">
-        <v>1.18</v>
+        <v>0.34</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-30T13:07:02.515Z</v>
+        <v>2026-07-30T13:24:02.720Z</v>
       </c>
     </row>
     <row r="219">
@@ -4116,10 +4116,10 @@
         <v>Passed</v>
       </c>
       <c r="D219">
-        <v>1.02</v>
+        <v>0.43</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-30T13:07:03.515Z</v>
+        <v>2026-07-30T13:24:03.720Z</v>
       </c>
     </row>
     <row r="220">
@@ -4133,10 +4133,10 @@
         <v>Passed</v>
       </c>
       <c r="D220">
-        <v>0.16</v>
+        <v>1.86</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-30T13:07:04.515Z</v>
+        <v>2026-07-30T13:24:04.720Z</v>
       </c>
     </row>
     <row r="221">
@@ -4150,10 +4150,10 @@
         <v>Passed</v>
       </c>
       <c r="D221">
-        <v>0.42</v>
+        <v>0.71</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-30T13:07:05.515Z</v>
+        <v>2026-07-30T13:24:05.720Z</v>
       </c>
     </row>
     <row r="222">
@@ -4167,10 +4167,10 @@
         <v>Passed</v>
       </c>
       <c r="D222">
-        <v>0.17</v>
+        <v>1.81</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-30T13:07:06.515Z</v>
+        <v>2026-07-30T13:24:06.720Z</v>
       </c>
     </row>
     <row r="223">
@@ -4184,10 +4184,10 @@
         <v>Passed</v>
       </c>
       <c r="D223">
-        <v>1.8</v>
+        <v>0.03</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-30T13:07:07.515Z</v>
+        <v>2026-07-30T13:24:07.720Z</v>
       </c>
     </row>
     <row r="224">
@@ -4201,10 +4201,10 @@
         <v>Passed</v>
       </c>
       <c r="D224">
-        <v>1.53</v>
+        <v>0.57</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-30T13:07:08.515Z</v>
+        <v>2026-07-30T13:24:08.720Z</v>
       </c>
     </row>
     <row r="225">
@@ -4218,10 +4218,10 @@
         <v>Passed</v>
       </c>
       <c r="D225">
-        <v>0.21</v>
+        <v>1.6</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-30T13:07:09.515Z</v>
+        <v>2026-07-30T13:24:09.720Z</v>
       </c>
     </row>
     <row r="226">
@@ -4235,10 +4235,10 @@
         <v>Passed</v>
       </c>
       <c r="D226">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-30T13:07:10.515Z</v>
+        <v>2026-07-30T13:24:10.720Z</v>
       </c>
     </row>
     <row r="227">
@@ -4252,10 +4252,10 @@
         <v>Passed</v>
       </c>
       <c r="D227">
-        <v>1.87</v>
+        <v>1.08</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-30T13:07:11.515Z</v>
+        <v>2026-07-30T13:24:11.720Z</v>
       </c>
     </row>
     <row r="228">
@@ -4269,10 +4269,10 @@
         <v>Passed</v>
       </c>
       <c r="D228">
-        <v>1.55</v>
+        <v>0.99</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-30T13:07:12.515Z</v>
+        <v>2026-07-30T13:24:12.720Z</v>
       </c>
     </row>
     <row r="229">
@@ -4286,10 +4286,10 @@
         <v>Passed</v>
       </c>
       <c r="D229">
-        <v>0.27</v>
+        <v>1.45</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-30T13:07:13.515Z</v>
+        <v>2026-07-30T13:24:13.720Z</v>
       </c>
     </row>
     <row r="230">
@@ -4303,10 +4303,10 @@
         <v>Passed</v>
       </c>
       <c r="D230">
-        <v>0.63</v>
+        <v>1.91</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-30T13:07:14.515Z</v>
+        <v>2026-07-30T13:24:14.720Z</v>
       </c>
     </row>
     <row r="231">
@@ -4320,10 +4320,10 @@
         <v>Passed</v>
       </c>
       <c r="D231">
-        <v>1.9</v>
+        <v>1.17</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-30T13:07:15.515Z</v>
+        <v>2026-07-30T13:24:15.720Z</v>
       </c>
     </row>
     <row r="232">
@@ -4337,10 +4337,10 @@
         <v>Passed</v>
       </c>
       <c r="D232">
-        <v>1.48</v>
+        <v>0.74</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-30T13:07:16.515Z</v>
+        <v>2026-07-30T13:24:16.720Z</v>
       </c>
     </row>
     <row r="233">
@@ -4354,10 +4354,10 @@
         <v>Passed</v>
       </c>
       <c r="D233">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-30T13:07:17.515Z</v>
+        <v>2026-07-30T13:24:17.720Z</v>
       </c>
     </row>
     <row r="234">
@@ -4371,10 +4371,10 @@
         <v>Passed</v>
       </c>
       <c r="D234">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-30T13:07:18.515Z</v>
+        <v>2026-07-30T13:24:18.720Z</v>
       </c>
     </row>
     <row r="235">
@@ -4388,10 +4388,10 @@
         <v>Passed</v>
       </c>
       <c r="D235">
-        <v>1.44</v>
+        <v>0.79</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-30T13:07:19.515Z</v>
+        <v>2026-07-30T13:24:19.720Z</v>
       </c>
     </row>
     <row r="236">
@@ -4405,10 +4405,10 @@
         <v>Passed</v>
       </c>
       <c r="D236">
-        <v>1.5</v>
+        <v>0.01</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-30T13:07:20.515Z</v>
+        <v>2026-07-30T13:24:20.720Z</v>
       </c>
     </row>
     <row r="237">
@@ -4422,10 +4422,10 @@
         <v>Passed</v>
       </c>
       <c r="D237">
-        <v>0.71</v>
+        <v>1.28</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-30T13:07:21.515Z</v>
+        <v>2026-07-30T13:24:21.720Z</v>
       </c>
     </row>
     <row r="238">
@@ -4439,10 +4439,10 @@
         <v>Passed</v>
       </c>
       <c r="D238">
-        <v>1.56</v>
+        <v>0.72</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-30T13:07:22.515Z</v>
+        <v>2026-07-30T13:24:22.720Z</v>
       </c>
     </row>
     <row r="239">
@@ -4456,10 +4456,10 @@
         <v>Passed</v>
       </c>
       <c r="D239">
-        <v>1.05</v>
+        <v>1.67</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-30T13:07:23.515Z</v>
+        <v>2026-07-30T13:24:23.720Z</v>
       </c>
     </row>
     <row r="240">
@@ -4473,10 +4473,10 @@
         <v>Passed</v>
       </c>
       <c r="D240">
-        <v>0.06</v>
+        <v>0.96</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-30T13:07:24.515Z</v>
+        <v>2026-07-30T13:24:24.720Z</v>
       </c>
     </row>
     <row r="241">
@@ -4490,10 +4490,10 @@
         <v>Passed</v>
       </c>
       <c r="D241">
-        <v>1.51</v>
+        <v>0.18</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-30T13:07:25.515Z</v>
+        <v>2026-07-30T13:24:25.720Z</v>
       </c>
     </row>
     <row r="242">
@@ -4507,10 +4507,10 @@
         <v>Passed</v>
       </c>
       <c r="D242">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-30T13:07:26.515Z</v>
+        <v>2026-07-30T13:24:26.720Z</v>
       </c>
     </row>
     <row r="243">
@@ -4524,10 +4524,10 @@
         <v>Passed</v>
       </c>
       <c r="D243">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-30T13:07:27.515Z</v>
+        <v>2026-07-30T13:24:27.720Z</v>
       </c>
     </row>
     <row r="244">
@@ -4541,10 +4541,10 @@
         <v>Passed</v>
       </c>
       <c r="D244">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-30T13:07:28.515Z</v>
+        <v>2026-07-30T13:24:28.720Z</v>
       </c>
     </row>
     <row r="245">
@@ -4558,10 +4558,10 @@
         <v>Passed</v>
       </c>
       <c r="D245">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-30T13:07:29.515Z</v>
+        <v>2026-07-30T13:24:29.720Z</v>
       </c>
     </row>
     <row r="246">
@@ -4575,10 +4575,10 @@
         <v>Passed</v>
       </c>
       <c r="D246">
-        <v>1.7</v>
+        <v>0.09</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-30T13:07:30.515Z</v>
+        <v>2026-07-30T13:24:30.720Z</v>
       </c>
     </row>
     <row r="247">
@@ -4592,10 +4592,10 @@
         <v>Passed</v>
       </c>
       <c r="D247">
-        <v>0.17</v>
+        <v>0.72</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-30T13:07:31.515Z</v>
+        <v>2026-07-30T13:24:31.720Z</v>
       </c>
     </row>
     <row r="248">
@@ -4609,10 +4609,10 @@
         <v>Passed</v>
       </c>
       <c r="D248">
-        <v>1.5</v>
+        <v>0.82</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-30T13:07:32.515Z</v>
+        <v>2026-07-30T13:24:32.720Z</v>
       </c>
     </row>
     <row r="249">
@@ -4626,10 +4626,10 @@
         <v>Passed</v>
       </c>
       <c r="D249">
-        <v>0.46</v>
+        <v>0.84</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-30T13:07:33.515Z</v>
+        <v>2026-07-30T13:24:33.720Z</v>
       </c>
     </row>
     <row r="250">
@@ -4643,10 +4643,10 @@
         <v>Passed</v>
       </c>
       <c r="D250">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-30T13:07:34.515Z</v>
+        <v>2026-07-30T13:24:34.720Z</v>
       </c>
     </row>
     <row r="251">
@@ -4660,10 +4660,10 @@
         <v>Passed</v>
       </c>
       <c r="D251">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-30T13:07:35.515Z</v>
+        <v>2026-07-30T13:24:35.720Z</v>
       </c>
     </row>
     <row r="252">
@@ -4677,10 +4677,10 @@
         <v>Passed</v>
       </c>
       <c r="D252">
-        <v>0.49</v>
+        <v>0.75</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-30T13:07:36.515Z</v>
+        <v>2026-07-30T13:24:36.720Z</v>
       </c>
     </row>
     <row r="253">
@@ -4694,10 +4694,10 @@
         <v>Passed</v>
       </c>
       <c r="D253">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-30T13:07:37.515Z</v>
+        <v>2026-07-30T13:24:37.720Z</v>
       </c>
     </row>
     <row r="254">
@@ -4711,10 +4711,10 @@
         <v>Passed</v>
       </c>
       <c r="D254">
-        <v>1.39</v>
+        <v>0.79</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-30T13:07:38.515Z</v>
+        <v>2026-07-30T13:24:38.720Z</v>
       </c>
     </row>
     <row r="255">
@@ -4728,10 +4728,10 @@
         <v>Passed</v>
       </c>
       <c r="D255">
-        <v>0.9</v>
+        <v>0.17</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-30T13:07:39.515Z</v>
+        <v>2026-07-30T13:24:39.720Z</v>
       </c>
     </row>
     <row r="256">
@@ -4745,10 +4745,10 @@
         <v>Passed</v>
       </c>
       <c r="D256">
-        <v>0.66</v>
+        <v>1.27</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-30T13:07:40.515Z</v>
+        <v>2026-07-30T13:24:40.720Z</v>
       </c>
     </row>
     <row r="257">
@@ -4762,10 +4762,10 @@
         <v>Passed</v>
       </c>
       <c r="D257">
-        <v>0.41</v>
+        <v>2</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-30T13:07:41.515Z</v>
+        <v>2026-07-30T13:24:41.720Z</v>
       </c>
     </row>
     <row r="258">
@@ -4779,10 +4779,10 @@
         <v>Passed</v>
       </c>
       <c r="D258">
-        <v>1.93</v>
+        <v>0.46</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-30T13:07:42.515Z</v>
+        <v>2026-07-30T13:24:42.720Z</v>
       </c>
     </row>
     <row r="259">
@@ -4796,10 +4796,10 @@
         <v>Passed</v>
       </c>
       <c r="D259">
-        <v>0.1</v>
+        <v>1.06</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-30T13:07:43.515Z</v>
+        <v>2026-07-30T13:24:43.720Z</v>
       </c>
     </row>
     <row r="260">
@@ -4813,10 +4813,10 @@
         <v>Passed</v>
       </c>
       <c r="D260">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-30T13:07:44.515Z</v>
+        <v>2026-07-30T13:24:44.720Z</v>
       </c>
     </row>
     <row r="261">
@@ -4830,10 +4830,10 @@
         <v>Passed</v>
       </c>
       <c r="D261">
-        <v>1.48</v>
+        <v>0.63</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-30T13:07:45.515Z</v>
+        <v>2026-07-30T13:24:45.720Z</v>
       </c>
     </row>
     <row r="262">
@@ -4847,10 +4847,10 @@
         <v>Passed</v>
       </c>
       <c r="D262">
-        <v>0.43</v>
+        <v>0.16</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-30T13:07:46.515Z</v>
+        <v>2026-07-30T13:24:46.720Z</v>
       </c>
     </row>
     <row r="263">
@@ -4864,10 +4864,10 @@
         <v>Passed</v>
       </c>
       <c r="D263">
-        <v>0.24</v>
+        <v>0.81</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-30T13:07:47.515Z</v>
+        <v>2026-07-30T13:24:47.720Z</v>
       </c>
     </row>
     <row r="264">
@@ -4881,10 +4881,10 @@
         <v>Passed</v>
       </c>
       <c r="D264">
-        <v>0.47</v>
+        <v>1.71</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-30T13:07:48.515Z</v>
+        <v>2026-07-30T13:24:48.720Z</v>
       </c>
     </row>
     <row r="265">
@@ -4898,10 +4898,10 @@
         <v>Passed</v>
       </c>
       <c r="D265">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-30T13:07:49.515Z</v>
+        <v>2026-07-30T13:24:49.720Z</v>
       </c>
     </row>
     <row r="266">
@@ -4915,10 +4915,10 @@
         <v>Passed</v>
       </c>
       <c r="D266">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-30T13:07:50.515Z</v>
+        <v>2026-07-30T13:24:50.720Z</v>
       </c>
     </row>
     <row r="267">
@@ -4932,10 +4932,10 @@
         <v>Passed</v>
       </c>
       <c r="D267">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-30T13:07:51.515Z</v>
+        <v>2026-07-30T13:24:51.720Z</v>
       </c>
     </row>
     <row r="268">
@@ -4949,10 +4949,10 @@
         <v>Passed</v>
       </c>
       <c r="D268">
-        <v>1.75</v>
+        <v>0.81</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-30T13:07:52.515Z</v>
+        <v>2026-07-30T13:24:52.720Z</v>
       </c>
     </row>
     <row r="269">
@@ -4966,10 +4966,10 @@
         <v>Passed</v>
       </c>
       <c r="D269">
-        <v>1.12</v>
+        <v>1.49</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-30T13:07:53.515Z</v>
+        <v>2026-07-30T13:24:53.720Z</v>
       </c>
     </row>
     <row r="270">
@@ -4983,10 +4983,10 @@
         <v>Passed</v>
       </c>
       <c r="D270">
-        <v>1.18</v>
+        <v>0.29</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-30T13:07:54.515Z</v>
+        <v>2026-07-30T13:24:54.720Z</v>
       </c>
     </row>
     <row r="271">
@@ -5000,10 +5000,10 @@
         <v>Passed</v>
       </c>
       <c r="D271">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-30T13:07:55.515Z</v>
+        <v>2026-07-30T13:24:55.720Z</v>
       </c>
     </row>
     <row r="272">
@@ -5017,10 +5017,10 @@
         <v>Passed</v>
       </c>
       <c r="D272">
-        <v>0.6</v>
+        <v>1.05</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-30T13:07:56.515Z</v>
+        <v>2026-07-30T13:24:56.720Z</v>
       </c>
     </row>
     <row r="273">
@@ -5034,10 +5034,10 @@
         <v>Passed</v>
       </c>
       <c r="D273">
-        <v>0.22</v>
+        <v>0.05</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-30T13:07:57.515Z</v>
+        <v>2026-07-30T13:24:57.720Z</v>
       </c>
     </row>
     <row r="274">
@@ -5051,10 +5051,10 @@
         <v>Passed</v>
       </c>
       <c r="D274">
-        <v>0.51</v>
+        <v>1.32</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-30T13:07:58.515Z</v>
+        <v>2026-07-30T13:24:58.720Z</v>
       </c>
     </row>
     <row r="275">
@@ -5068,10 +5068,10 @@
         <v>Passed</v>
       </c>
       <c r="D275">
-        <v>1.37</v>
+        <v>0.62</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-30T13:07:59.515Z</v>
+        <v>2026-07-30T13:24:59.720Z</v>
       </c>
     </row>
     <row r="276">
@@ -5085,10 +5085,10 @@
         <v>Passed</v>
       </c>
       <c r="D276">
-        <v>0.5</v>
+        <v>1.58</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-30T13:08:00.515Z</v>
+        <v>2026-07-30T13:25:00.720Z</v>
       </c>
     </row>
     <row r="277">
@@ -5102,10 +5102,10 @@
         <v>Passed</v>
       </c>
       <c r="D277">
-        <v>0.6</v>
+        <v>1.21</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-30T13:08:01.515Z</v>
+        <v>2026-07-30T13:25:01.720Z</v>
       </c>
     </row>
     <row r="278">
@@ -5119,10 +5119,10 @@
         <v>Passed</v>
       </c>
       <c r="D278">
-        <v>0.59</v>
+        <v>1.82</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-30T13:08:02.515Z</v>
+        <v>2026-07-30T13:25:02.720Z</v>
       </c>
     </row>
     <row r="279">
@@ -5136,10 +5136,10 @@
         <v>Passed</v>
       </c>
       <c r="D279">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-30T13:08:03.515Z</v>
+        <v>2026-07-30T13:25:03.720Z</v>
       </c>
     </row>
     <row r="280">
@@ -5153,10 +5153,10 @@
         <v>Passed</v>
       </c>
       <c r="D280">
-        <v>1.41</v>
+        <v>0.23</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-30T13:08:04.515Z</v>
+        <v>2026-07-30T13:25:04.720Z</v>
       </c>
     </row>
     <row r="281">
@@ -5170,10 +5170,10 @@
         <v>Passed</v>
       </c>
       <c r="D281">
-        <v>0.27</v>
+        <v>1.36</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-30T13:08:05.515Z</v>
+        <v>2026-07-30T13:25:05.720Z</v>
       </c>
     </row>
     <row r="282">
@@ -5187,10 +5187,10 @@
         <v>Passed</v>
       </c>
       <c r="D282">
-        <v>1.96</v>
+        <v>1.07</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-30T13:08:06.515Z</v>
+        <v>2026-07-30T13:25:06.720Z</v>
       </c>
     </row>
     <row r="283">
@@ -5204,10 +5204,10 @@
         <v>Passed</v>
       </c>
       <c r="D283">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-30T13:08:07.515Z</v>
+        <v>2026-07-30T13:25:07.720Z</v>
       </c>
     </row>
     <row r="284">
@@ -5221,10 +5221,10 @@
         <v>Passed</v>
       </c>
       <c r="D284">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-30T13:08:08.515Z</v>
+        <v>2026-07-30T13:25:08.720Z</v>
       </c>
     </row>
     <row r="285">
@@ -5238,10 +5238,10 @@
         <v>Passed</v>
       </c>
       <c r="D285">
-        <v>1.26</v>
+        <v>0.81</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-30T13:08:09.515Z</v>
+        <v>2026-07-30T13:25:09.720Z</v>
       </c>
     </row>
     <row r="286">
@@ -5255,10 +5255,10 @@
         <v>Passed</v>
       </c>
       <c r="D286">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-30T13:08:10.515Z</v>
+        <v>2026-07-30T13:25:10.720Z</v>
       </c>
     </row>
     <row r="287">
@@ -5272,10 +5272,10 @@
         <v>Passed</v>
       </c>
       <c r="D287">
-        <v>1.1</v>
+        <v>1.64</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-30T13:08:11.515Z</v>
+        <v>2026-07-30T13:25:11.720Z</v>
       </c>
     </row>
     <row r="288">
@@ -5289,10 +5289,10 @@
         <v>Passed</v>
       </c>
       <c r="D288">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-30T13:08:12.515Z</v>
+        <v>2026-07-30T13:25:12.720Z</v>
       </c>
     </row>
     <row r="289">
@@ -5306,10 +5306,10 @@
         <v>Passed</v>
       </c>
       <c r="D289">
-        <v>0.59</v>
+        <v>0.79</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-30T13:08:13.515Z</v>
+        <v>2026-07-30T13:25:13.720Z</v>
       </c>
     </row>
     <row r="290">
@@ -5323,10 +5323,10 @@
         <v>Passed</v>
       </c>
       <c r="D290">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-30T13:08:14.515Z</v>
+        <v>2026-07-30T13:25:14.720Z</v>
       </c>
     </row>
     <row r="291">
@@ -5340,10 +5340,10 @@
         <v>Passed</v>
       </c>
       <c r="D291">
-        <v>1.58</v>
+        <v>0.27</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-30T13:08:15.515Z</v>
+        <v>2026-07-30T13:25:15.720Z</v>
       </c>
     </row>
     <row r="292">
@@ -5357,10 +5357,10 @@
         <v>Passed</v>
       </c>
       <c r="D292">
-        <v>0.9</v>
+        <v>1.31</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-30T13:08:16.515Z</v>
+        <v>2026-07-30T13:25:16.720Z</v>
       </c>
     </row>
     <row r="293">
@@ -5374,10 +5374,10 @@
         <v>Passed</v>
       </c>
       <c r="D293">
-        <v>1.17</v>
+        <v>0.53</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-30T13:08:17.515Z</v>
+        <v>2026-07-30T13:25:17.720Z</v>
       </c>
     </row>
     <row r="294">
@@ -5391,10 +5391,10 @@
         <v>Passed</v>
       </c>
       <c r="D294">
-        <v>1.84</v>
+        <v>0.31</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-30T13:08:18.515Z</v>
+        <v>2026-07-30T13:25:18.720Z</v>
       </c>
     </row>
     <row r="295">
@@ -5408,10 +5408,10 @@
         <v>Passed</v>
       </c>
       <c r="D295">
-        <v>0.82</v>
+        <v>0.6</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-30T13:08:19.515Z</v>
+        <v>2026-07-30T13:25:19.720Z</v>
       </c>
     </row>
     <row r="296">
@@ -5425,10 +5425,10 @@
         <v>Passed</v>
       </c>
       <c r="D296">
-        <v>1.46</v>
+        <v>0.6</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-30T13:08:20.515Z</v>
+        <v>2026-07-30T13:25:20.720Z</v>
       </c>
     </row>
     <row r="297">
@@ -5442,10 +5442,10 @@
         <v>Passed</v>
       </c>
       <c r="D297">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-30T13:08:21.515Z</v>
+        <v>2026-07-30T13:25:21.720Z</v>
       </c>
     </row>
     <row r="298">
@@ -5459,10 +5459,10 @@
         <v>Passed</v>
       </c>
       <c r="D298">
-        <v>1.97</v>
+        <v>0.17</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-30T13:08:22.515Z</v>
+        <v>2026-07-30T13:25:22.720Z</v>
       </c>
     </row>
     <row r="299">
@@ -5476,10 +5476,10 @@
         <v>Passed</v>
       </c>
       <c r="D299">
-        <v>1.72</v>
+        <v>0.85</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-30T13:08:23.515Z</v>
+        <v>2026-07-30T13:25:23.720Z</v>
       </c>
     </row>
     <row r="300">
@@ -5493,10 +5493,10 @@
         <v>Passed</v>
       </c>
       <c r="D300">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-30T13:08:24.515Z</v>
+        <v>2026-07-30T13:25:24.720Z</v>
       </c>
     </row>
     <row r="301">
@@ -5510,10 +5510,10 @@
         <v>Passed</v>
       </c>
       <c r="D301">
-        <v>0.45</v>
+        <v>1.59</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-30T13:08:25.515Z</v>
+        <v>2026-07-30T13:25:25.720Z</v>
       </c>
     </row>
     <row r="302">
@@ -5527,10 +5527,10 @@
         <v>Passed</v>
       </c>
       <c r="D302">
-        <v>0.11</v>
+        <v>1.57</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-30T13:08:26.515Z</v>
+        <v>2026-07-30T13:25:26.720Z</v>
       </c>
     </row>
     <row r="303">
@@ -5544,10 +5544,10 @@
         <v>Passed</v>
       </c>
       <c r="D303">
-        <v>1.43</v>
+        <v>0.4</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-30T13:08:27.515Z</v>
+        <v>2026-07-30T13:25:27.720Z</v>
       </c>
     </row>
     <row r="304">
@@ -5561,10 +5561,10 @@
         <v>Passed</v>
       </c>
       <c r="D304">
-        <v>0.04</v>
+        <v>0.53</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-30T13:08:28.515Z</v>
+        <v>2026-07-30T13:25:28.720Z</v>
       </c>
     </row>
     <row r="305">
@@ -5578,10 +5578,10 @@
         <v>Passed</v>
       </c>
       <c r="D305">
-        <v>1.78</v>
+        <v>0.78</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-30T13:08:29.515Z</v>
+        <v>2026-07-30T13:25:29.720Z</v>
       </c>
     </row>
     <row r="306">
@@ -5595,10 +5595,10 @@
         <v>Passed</v>
       </c>
       <c r="D306">
-        <v>0.78</v>
+        <v>1.71</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-30T13:08:30.515Z</v>
+        <v>2026-07-30T13:25:30.720Z</v>
       </c>
     </row>
     <row r="307">
@@ -5612,10 +5612,10 @@
         <v>Passed</v>
       </c>
       <c r="D307">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-30T13:08:31.515Z</v>
+        <v>2026-07-30T13:25:31.720Z</v>
       </c>
     </row>
     <row r="308">
@@ -5629,10 +5629,10 @@
         <v>Passed</v>
       </c>
       <c r="D308">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-30T13:08:32.515Z</v>
+        <v>2026-07-30T13:25:32.720Z</v>
       </c>
     </row>
     <row r="309">
@@ -5646,10 +5646,10 @@
         <v>Passed</v>
       </c>
       <c r="D309">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-30T13:08:33.515Z</v>
+        <v>2026-07-30T13:25:33.720Z</v>
       </c>
     </row>
     <row r="310">
@@ -5663,10 +5663,10 @@
         <v>Passed</v>
       </c>
       <c r="D310">
-        <v>1.69</v>
+        <v>0.76</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-30T13:08:34.515Z</v>
+        <v>2026-07-30T13:25:34.720Z</v>
       </c>
     </row>
     <row r="311">
@@ -5680,10 +5680,10 @@
         <v>Passed</v>
       </c>
       <c r="D311">
-        <v>0.66</v>
+        <v>1.74</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-30T13:08:35.515Z</v>
+        <v>2026-07-30T13:25:35.720Z</v>
       </c>
     </row>
     <row r="312">
@@ -5697,10 +5697,10 @@
         <v>Passed</v>
       </c>
       <c r="D312">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-30T13:08:36.515Z</v>
+        <v>2026-07-30T13:25:36.720Z</v>
       </c>
     </row>
     <row r="313">
@@ -5714,10 +5714,10 @@
         <v>Passed</v>
       </c>
       <c r="D313">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-30T13:08:37.515Z</v>
+        <v>2026-07-30T13:25:37.720Z</v>
       </c>
     </row>
     <row r="314">
@@ -5731,10 +5731,10 @@
         <v>Passed</v>
       </c>
       <c r="D314">
-        <v>1.17</v>
+        <v>0.79</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-30T13:08:38.515Z</v>
+        <v>2026-07-30T13:25:38.720Z</v>
       </c>
     </row>
     <row r="315">
@@ -5748,10 +5748,10 @@
         <v>Passed</v>
       </c>
       <c r="D315">
-        <v>0.1</v>
+        <v>0.63</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-30T13:08:39.515Z</v>
+        <v>2026-07-30T13:25:39.720Z</v>
       </c>
     </row>
     <row r="316">
@@ -5765,10 +5765,10 @@
         <v>Passed</v>
       </c>
       <c r="D316">
-        <v>0.58</v>
+        <v>1.77</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-30T13:08:40.515Z</v>
+        <v>2026-07-30T13:25:40.720Z</v>
       </c>
     </row>
     <row r="317">
@@ -5782,10 +5782,10 @@
         <v>Passed</v>
       </c>
       <c r="D317">
-        <v>0.18</v>
+        <v>1.09</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-30T13:08:41.515Z</v>
+        <v>2026-07-30T13:25:41.720Z</v>
       </c>
     </row>
     <row r="318">
@@ -5799,10 +5799,10 @@
         <v>Passed</v>
       </c>
       <c r="D318">
-        <v>1.46</v>
+        <v>0.21</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-30T13:08:42.515Z</v>
+        <v>2026-07-30T13:25:42.720Z</v>
       </c>
     </row>
     <row r="319">
@@ -5816,10 +5816,10 @@
         <v>Passed</v>
       </c>
       <c r="D319">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-30T13:08:43.515Z</v>
+        <v>2026-07-30T13:25:43.720Z</v>
       </c>
     </row>
     <row r="320">
@@ -5833,10 +5833,10 @@
         <v>Passed</v>
       </c>
       <c r="D320">
-        <v>1.42</v>
+        <v>0.51</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-30T13:08:44.515Z</v>
+        <v>2026-07-30T13:25:44.720Z</v>
       </c>
     </row>
     <row r="321">
@@ -5850,10 +5850,10 @@
         <v>Passed</v>
       </c>
       <c r="D321">
-        <v>1.14</v>
+        <v>1.86</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-30T13:08:45.515Z</v>
+        <v>2026-07-30T13:25:45.720Z</v>
       </c>
     </row>
     <row r="322">
@@ -5867,10 +5867,10 @@
         <v>Passed</v>
       </c>
       <c r="D322">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-30T13:08:46.515Z</v>
+        <v>2026-07-30T13:25:46.720Z</v>
       </c>
     </row>
     <row r="323">
@@ -5884,10 +5884,10 @@
         <v>Passed</v>
       </c>
       <c r="D323">
-        <v>0.34</v>
+        <v>0.99</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-30T13:08:47.515Z</v>
+        <v>2026-07-30T13:25:47.720Z</v>
       </c>
     </row>
     <row r="324">
@@ -5901,10 +5901,10 @@
         <v>Passed</v>
       </c>
       <c r="D324">
-        <v>1.58</v>
+        <v>0.11</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-30T13:08:48.515Z</v>
+        <v>2026-07-30T13:25:48.720Z</v>
       </c>
     </row>
     <row r="325">
@@ -5918,10 +5918,10 @@
         <v>Passed</v>
       </c>
       <c r="D325">
-        <v>0.12</v>
+        <v>0.07</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-30T13:08:49.515Z</v>
+        <v>2026-07-30T13:25:49.720Z</v>
       </c>
     </row>
     <row r="326">
@@ -5935,10 +5935,10 @@
         <v>Passed</v>
       </c>
       <c r="D326">
-        <v>1.9</v>
+        <v>1.32</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-30T13:08:50.515Z</v>
+        <v>2026-07-30T13:25:50.720Z</v>
       </c>
     </row>
     <row r="327">
@@ -5952,10 +5952,10 @@
         <v>Passed</v>
       </c>
       <c r="D327">
-        <v>0.12</v>
+        <v>1.81</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-30T13:08:51.515Z</v>
+        <v>2026-07-30T13:25:51.720Z</v>
       </c>
     </row>
     <row r="328">
@@ -5969,10 +5969,10 @@
         <v>Passed</v>
       </c>
       <c r="D328">
-        <v>1.09</v>
+        <v>0.06</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-30T13:08:52.515Z</v>
+        <v>2026-07-30T13:25:52.720Z</v>
       </c>
     </row>
     <row r="329">
@@ -5986,10 +5986,10 @@
         <v>Passed</v>
       </c>
       <c r="D329">
-        <v>1.94</v>
+        <v>1.19</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-30T13:08:53.515Z</v>
+        <v>2026-07-30T13:25:53.720Z</v>
       </c>
     </row>
     <row r="330">
@@ -6003,10 +6003,10 @@
         <v>Passed</v>
       </c>
       <c r="D330">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-30T13:08:54.515Z</v>
+        <v>2026-07-30T13:25:54.720Z</v>
       </c>
     </row>
     <row r="331">
@@ -6020,10 +6020,10 @@
         <v>Passed</v>
       </c>
       <c r="D331">
-        <v>1.08</v>
+        <v>1.58</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-30T13:08:55.515Z</v>
+        <v>2026-07-30T13:25:55.720Z</v>
       </c>
     </row>
     <row r="332">
@@ -6034,13 +6034,13 @@
         <v>Verify Security functionality module 331</v>
       </c>
       <c r="C332" t="str">
-        <v>Failed</v>
+        <v>Passed</v>
       </c>
       <c r="D332">
-        <v>1.16</v>
+        <v>0.31</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-30T13:08:56.515Z</v>
+        <v>2026-07-30T13:25:56.720Z</v>
       </c>
     </row>
     <row r="333">
@@ -6054,10 +6054,10 @@
         <v>Passed</v>
       </c>
       <c r="D333">
-        <v>1.43</v>
+        <v>0.55</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-30T13:08:57.515Z</v>
+        <v>2026-07-30T13:25:57.720Z</v>
       </c>
     </row>
     <row r="334">
@@ -6071,10 +6071,10 @@
         <v>Passed</v>
       </c>
       <c r="D334">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-30T13:08:58.515Z</v>
+        <v>2026-07-30T13:25:58.720Z</v>
       </c>
     </row>
     <row r="335">
@@ -6088,10 +6088,10 @@
         <v>Passed</v>
       </c>
       <c r="D335">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-30T13:08:59.515Z</v>
+        <v>2026-07-30T13:25:59.720Z</v>
       </c>
     </row>
     <row r="336">
@@ -6105,10 +6105,10 @@
         <v>Passed</v>
       </c>
       <c r="D336">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-30T13:09:00.515Z</v>
+        <v>2026-07-30T13:26:00.720Z</v>
       </c>
     </row>
     <row r="337">
@@ -6122,10 +6122,10 @@
         <v>Passed</v>
       </c>
       <c r="D337">
-        <v>1.45</v>
+        <v>0.84</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-30T13:09:01.515Z</v>
+        <v>2026-07-30T13:26:01.720Z</v>
       </c>
     </row>
     <row r="338">
@@ -6139,10 +6139,10 @@
         <v>Passed</v>
       </c>
       <c r="D338">
-        <v>0.21</v>
+        <v>1.2</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-30T13:09:02.515Z</v>
+        <v>2026-07-30T13:26:02.720Z</v>
       </c>
     </row>
     <row r="339">
@@ -6156,10 +6156,10 @@
         <v>Passed</v>
       </c>
       <c r="D339">
-        <v>1.61</v>
+        <v>0.44</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-30T13:09:03.515Z</v>
+        <v>2026-07-30T13:26:03.720Z</v>
       </c>
     </row>
     <row r="340">
@@ -6173,10 +6173,10 @@
         <v>Passed</v>
       </c>
       <c r="D340">
-        <v>0.89</v>
+        <v>1.76</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-30T13:09:04.515Z</v>
+        <v>2026-07-30T13:26:04.720Z</v>
       </c>
     </row>
     <row r="341">
@@ -6190,10 +6190,10 @@
         <v>Passed</v>
       </c>
       <c r="D341">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-30T13:09:05.515Z</v>
+        <v>2026-07-30T13:26:05.720Z</v>
       </c>
     </row>
     <row r="342">
@@ -6207,10 +6207,10 @@
         <v>Passed</v>
       </c>
       <c r="D342">
-        <v>1.57</v>
+        <v>1.08</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-30T13:09:06.515Z</v>
+        <v>2026-07-30T13:26:06.720Z</v>
       </c>
     </row>
     <row r="343">
@@ -6224,10 +6224,10 @@
         <v>Passed</v>
       </c>
       <c r="D343">
-        <v>1.09</v>
+        <v>0.27</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-30T13:09:07.515Z</v>
+        <v>2026-07-30T13:26:07.720Z</v>
       </c>
     </row>
     <row r="344">
@@ -6241,10 +6241,10 @@
         <v>Passed</v>
       </c>
       <c r="D344">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-30T13:09:08.515Z</v>
+        <v>2026-07-30T13:26:08.720Z</v>
       </c>
     </row>
     <row r="345">
@@ -6258,10 +6258,10 @@
         <v>Passed</v>
       </c>
       <c r="D345">
-        <v>1.1</v>
+        <v>0.05</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-30T13:09:09.515Z</v>
+        <v>2026-07-30T13:26:09.720Z</v>
       </c>
     </row>
     <row r="346">
@@ -6275,10 +6275,10 @@
         <v>Passed</v>
       </c>
       <c r="D346">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-30T13:09:10.515Z</v>
+        <v>2026-07-30T13:26:10.720Z</v>
       </c>
     </row>
     <row r="347">
@@ -6292,10 +6292,10 @@
         <v>Passed</v>
       </c>
       <c r="D347">
-        <v>0.49</v>
+        <v>1.19</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-30T13:09:11.515Z</v>
+        <v>2026-07-30T13:26:11.720Z</v>
       </c>
     </row>
     <row r="348">
@@ -6309,10 +6309,10 @@
         <v>Passed</v>
       </c>
       <c r="D348">
-        <v>0.5</v>
+        <v>1.96</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-30T13:09:12.515Z</v>
+        <v>2026-07-30T13:26:12.720Z</v>
       </c>
     </row>
     <row r="349">
@@ -6326,10 +6326,10 @@
         <v>Passed</v>
       </c>
       <c r="D349">
-        <v>1.67</v>
+        <v>0.89</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-30T13:09:13.515Z</v>
+        <v>2026-07-30T13:26:13.720Z</v>
       </c>
     </row>
     <row r="350">
@@ -6343,10 +6343,10 @@
         <v>Passed</v>
       </c>
       <c r="D350">
-        <v>1.97</v>
+        <v>0.68</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-30T13:09:14.515Z</v>
+        <v>2026-07-30T13:26:14.720Z</v>
       </c>
     </row>
     <row r="351">
@@ -6360,10 +6360,10 @@
         <v>Passed</v>
       </c>
       <c r="D351">
-        <v>1.5</v>
+        <v>0.86</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-30T13:09:15.515Z</v>
+        <v>2026-07-30T13:26:15.720Z</v>
       </c>
     </row>
     <row r="352">
@@ -6377,10 +6377,10 @@
         <v>Passed</v>
       </c>
       <c r="D352">
-        <v>1.08</v>
+        <v>1.99</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-30T13:09:16.515Z</v>
+        <v>2026-07-30T13:26:16.720Z</v>
       </c>
     </row>
     <row r="353">
@@ -6394,10 +6394,10 @@
         <v>Passed</v>
       </c>
       <c r="D353">
-        <v>0.79</v>
+        <v>1.45</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-30T13:09:17.515Z</v>
+        <v>2026-07-30T13:26:17.720Z</v>
       </c>
     </row>
     <row r="354">
@@ -6411,10 +6411,10 @@
         <v>Passed</v>
       </c>
       <c r="D354">
-        <v>0.62</v>
+        <v>1.89</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-30T13:09:18.515Z</v>
+        <v>2026-07-30T13:26:18.720Z</v>
       </c>
     </row>
     <row r="355">
@@ -6428,10 +6428,10 @@
         <v>Passed</v>
       </c>
       <c r="D355">
-        <v>0.54</v>
+        <v>1.3</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-30T13:09:19.515Z</v>
+        <v>2026-07-30T13:26:19.720Z</v>
       </c>
     </row>
     <row r="356">
@@ -6445,10 +6445,10 @@
         <v>Passed</v>
       </c>
       <c r="D356">
-        <v>0.8</v>
+        <v>1.91</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-30T13:09:20.515Z</v>
+        <v>2026-07-30T13:26:20.720Z</v>
       </c>
     </row>
     <row r="357">
@@ -6462,10 +6462,10 @@
         <v>Passed</v>
       </c>
       <c r="D357">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-30T13:09:21.515Z</v>
+        <v>2026-07-30T13:26:21.720Z</v>
       </c>
     </row>
     <row r="358">
@@ -6479,10 +6479,10 @@
         <v>Passed</v>
       </c>
       <c r="D358">
-        <v>1.55</v>
+        <v>0.99</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-30T13:09:22.515Z</v>
+        <v>2026-07-30T13:26:22.720Z</v>
       </c>
     </row>
     <row r="359">
@@ -6496,10 +6496,10 @@
         <v>Passed</v>
       </c>
       <c r="D359">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-30T13:09:23.515Z</v>
+        <v>2026-07-30T13:26:23.720Z</v>
       </c>
     </row>
     <row r="360">
@@ -6513,10 +6513,10 @@
         <v>Passed</v>
       </c>
       <c r="D360">
-        <v>0.54</v>
+        <v>0.16</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-30T13:09:24.515Z</v>
+        <v>2026-07-30T13:26:24.720Z</v>
       </c>
     </row>
     <row r="361">
@@ -6530,10 +6530,10 @@
         <v>Passed</v>
       </c>
       <c r="D361">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-30T13:09:25.515Z</v>
+        <v>2026-07-30T13:26:25.720Z</v>
       </c>
     </row>
     <row r="362">
@@ -6547,10 +6547,10 @@
         <v>Passed</v>
       </c>
       <c r="D362">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-30T13:09:26.515Z</v>
+        <v>2026-07-30T13:26:26.720Z</v>
       </c>
     </row>
     <row r="363">
@@ -6564,10 +6564,10 @@
         <v>Passed</v>
       </c>
       <c r="D363">
-        <v>1.57</v>
+        <v>0.44</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-30T13:09:27.515Z</v>
+        <v>2026-07-30T13:26:27.720Z</v>
       </c>
     </row>
     <row r="364">
@@ -6581,10 +6581,10 @@
         <v>Passed</v>
       </c>
       <c r="D364">
-        <v>1.32</v>
+        <v>0.03</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-30T13:09:28.515Z</v>
+        <v>2026-07-30T13:26:28.720Z</v>
       </c>
     </row>
     <row r="365">
@@ -6598,10 +6598,10 @@
         <v>Passed</v>
       </c>
       <c r="D365">
-        <v>0.24</v>
+        <v>1.8</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-30T13:09:29.515Z</v>
+        <v>2026-07-30T13:26:29.720Z</v>
       </c>
     </row>
     <row r="366">
@@ -6615,10 +6615,10 @@
         <v>Passed</v>
       </c>
       <c r="D366">
-        <v>1.62</v>
+        <v>0.28</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-30T13:09:30.515Z</v>
+        <v>2026-07-30T13:26:30.720Z</v>
       </c>
     </row>
     <row r="367">
@@ -6632,10 +6632,10 @@
         <v>Passed</v>
       </c>
       <c r="D367">
-        <v>0.93</v>
+        <v>1.39</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-30T13:09:31.515Z</v>
+        <v>2026-07-30T13:26:31.720Z</v>
       </c>
     </row>
     <row r="368">
@@ -6649,10 +6649,10 @@
         <v>Passed</v>
       </c>
       <c r="D368">
-        <v>0.97</v>
+        <v>1.58</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-30T13:09:32.515Z</v>
+        <v>2026-07-30T13:26:32.720Z</v>
       </c>
     </row>
     <row r="369">
@@ -6666,10 +6666,10 @@
         <v>Passed</v>
       </c>
       <c r="D369">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-30T13:09:33.515Z</v>
+        <v>2026-07-30T13:26:33.720Z</v>
       </c>
     </row>
     <row r="370">
@@ -6683,10 +6683,10 @@
         <v>Passed</v>
       </c>
       <c r="D370">
-        <v>0.4</v>
+        <v>1.72</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-30T13:09:34.515Z</v>
+        <v>2026-07-30T13:26:34.720Z</v>
       </c>
     </row>
     <row r="371">
@@ -6700,10 +6700,10 @@
         <v>Passed</v>
       </c>
       <c r="D371">
-        <v>1.65</v>
+        <v>0.01</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-30T13:09:35.515Z</v>
+        <v>2026-07-30T13:26:35.720Z</v>
       </c>
     </row>
     <row r="372">
@@ -6717,10 +6717,10 @@
         <v>Passed</v>
       </c>
       <c r="D372">
-        <v>1.91</v>
+        <v>0.77</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-30T13:09:36.515Z</v>
+        <v>2026-07-30T13:26:36.720Z</v>
       </c>
     </row>
     <row r="373">
@@ -6734,10 +6734,10 @@
         <v>Passed</v>
       </c>
       <c r="D373">
-        <v>1.4</v>
+        <v>0.46</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-30T13:09:37.515Z</v>
+        <v>2026-07-30T13:26:37.720Z</v>
       </c>
     </row>
     <row r="374">
@@ -6751,10 +6751,10 @@
         <v>Passed</v>
       </c>
       <c r="D374">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-30T13:09:38.515Z</v>
+        <v>2026-07-30T13:26:38.720Z</v>
       </c>
     </row>
     <row r="375">
@@ -6768,10 +6768,10 @@
         <v>Passed</v>
       </c>
       <c r="D375">
-        <v>0.23</v>
+        <v>1.57</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-30T13:09:39.515Z</v>
+        <v>2026-07-30T13:26:39.720Z</v>
       </c>
     </row>
     <row r="376">
@@ -6785,10 +6785,10 @@
         <v>Passed</v>
       </c>
       <c r="D376">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-30T13:09:40.515Z</v>
+        <v>2026-07-30T13:26:40.720Z</v>
       </c>
     </row>
     <row r="377">
@@ -6802,10 +6802,10 @@
         <v>Passed</v>
       </c>
       <c r="D377">
-        <v>0.88</v>
+        <v>1.14</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-30T13:09:41.515Z</v>
+        <v>2026-07-30T13:26:41.720Z</v>
       </c>
     </row>
     <row r="378">
@@ -6819,10 +6819,10 @@
         <v>Passed</v>
       </c>
       <c r="D378">
-        <v>0.25</v>
+        <v>0.74</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-30T13:09:42.515Z</v>
+        <v>2026-07-30T13:26:42.720Z</v>
       </c>
     </row>
     <row r="379">
@@ -6836,10 +6836,10 @@
         <v>Passed</v>
       </c>
       <c r="D379">
-        <v>0.7</v>
+        <v>1.99</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-30T13:09:43.515Z</v>
+        <v>2026-07-30T13:26:43.720Z</v>
       </c>
     </row>
     <row r="380">
@@ -6853,10 +6853,10 @@
         <v>Passed</v>
       </c>
       <c r="D380">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-30T13:09:44.515Z</v>
+        <v>2026-07-30T13:26:44.720Z</v>
       </c>
     </row>
     <row r="381">
@@ -6870,10 +6870,10 @@
         <v>Passed</v>
       </c>
       <c r="D381">
-        <v>0.05</v>
+        <v>0.91</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-30T13:09:45.515Z</v>
+        <v>2026-07-30T13:26:45.720Z</v>
       </c>
     </row>
     <row r="382">
@@ -6887,10 +6887,10 @@
         <v>Passed</v>
       </c>
       <c r="D382">
-        <v>0.85</v>
+        <v>1.42</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-30T13:09:46.515Z</v>
+        <v>2026-07-30T13:26:46.720Z</v>
       </c>
     </row>
     <row r="383">
@@ -6904,10 +6904,10 @@
         <v>Passed</v>
       </c>
       <c r="D383">
-        <v>1.99</v>
+        <v>0.16</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-30T13:09:47.515Z</v>
+        <v>2026-07-30T13:26:47.720Z</v>
       </c>
     </row>
     <row r="384">
@@ -6921,10 +6921,10 @@
         <v>Passed</v>
       </c>
       <c r="D384">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-30T13:09:48.515Z</v>
+        <v>2026-07-30T13:26:48.720Z</v>
       </c>
     </row>
     <row r="385">
@@ -6938,10 +6938,10 @@
         <v>Passed</v>
       </c>
       <c r="D385">
-        <v>0.04</v>
+        <v>1.26</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-30T13:09:49.515Z</v>
+        <v>2026-07-30T13:26:49.720Z</v>
       </c>
     </row>
     <row r="386">
@@ -6955,10 +6955,10 @@
         <v>Passed</v>
       </c>
       <c r="D386">
-        <v>1.91</v>
+        <v>0.65</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-30T13:09:50.515Z</v>
+        <v>2026-07-30T13:26:50.720Z</v>
       </c>
     </row>
     <row r="387">
@@ -6972,10 +6972,10 @@
         <v>Passed</v>
       </c>
       <c r="D387">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-30T13:09:51.515Z</v>
+        <v>2026-07-30T13:26:51.720Z</v>
       </c>
     </row>
     <row r="388">
@@ -6989,10 +6989,10 @@
         <v>Passed</v>
       </c>
       <c r="D388">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-30T13:09:52.515Z</v>
+        <v>2026-07-30T13:26:52.720Z</v>
       </c>
     </row>
     <row r="389">
@@ -7006,10 +7006,10 @@
         <v>Passed</v>
       </c>
       <c r="D389">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-30T13:09:53.515Z</v>
+        <v>2026-07-30T13:26:53.720Z</v>
       </c>
     </row>
     <row r="390">
@@ -7023,10 +7023,10 @@
         <v>Passed</v>
       </c>
       <c r="D390">
-        <v>0.89</v>
+        <v>0.35</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-30T13:09:54.515Z</v>
+        <v>2026-07-30T13:26:54.720Z</v>
       </c>
     </row>
     <row r="391">
@@ -7040,10 +7040,10 @@
         <v>Passed</v>
       </c>
       <c r="D391">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-30T13:09:55.515Z</v>
+        <v>2026-07-30T13:26:55.720Z</v>
       </c>
     </row>
     <row r="392">
@@ -7057,10 +7057,10 @@
         <v>Passed</v>
       </c>
       <c r="D392">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-30T13:09:56.515Z</v>
+        <v>2026-07-30T13:26:56.720Z</v>
       </c>
     </row>
     <row r="393">
@@ -7074,10 +7074,10 @@
         <v>Passed</v>
       </c>
       <c r="D393">
-        <v>1.39</v>
+        <v>0.04</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-30T13:09:57.515Z</v>
+        <v>2026-07-30T13:26:57.720Z</v>
       </c>
     </row>
     <row r="394">
@@ -7091,10 +7091,10 @@
         <v>Passed</v>
       </c>
       <c r="D394">
-        <v>0.13</v>
+        <v>1.37</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-30T13:09:58.515Z</v>
+        <v>2026-07-30T13:26:58.720Z</v>
       </c>
     </row>
     <row r="395">
@@ -7108,10 +7108,10 @@
         <v>Passed</v>
       </c>
       <c r="D395">
-        <v>0.52</v>
+        <v>0.95</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-30T13:09:59.515Z</v>
+        <v>2026-07-30T13:26:59.720Z</v>
       </c>
     </row>
     <row r="396">
@@ -7125,10 +7125,10 @@
         <v>Passed</v>
       </c>
       <c r="D396">
-        <v>1.06</v>
+        <v>0.67</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-30T13:10:00.515Z</v>
+        <v>2026-07-30T13:27:00.720Z</v>
       </c>
     </row>
     <row r="397">
@@ -7142,10 +7142,10 @@
         <v>Passed</v>
       </c>
       <c r="D397">
-        <v>1.54</v>
+        <v>0.92</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-30T13:10:01.515Z</v>
+        <v>2026-07-30T13:27:01.720Z</v>
       </c>
     </row>
     <row r="398">
@@ -7159,10 +7159,10 @@
         <v>Passed</v>
       </c>
       <c r="D398">
-        <v>1.7</v>
+        <v>0.42</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-30T13:10:02.515Z</v>
+        <v>2026-07-30T13:27:02.720Z</v>
       </c>
     </row>
     <row r="399">
@@ -7176,10 +7176,10 @@
         <v>Passed</v>
       </c>
       <c r="D399">
-        <v>1.85</v>
+        <v>0.64</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-30T13:10:03.515Z</v>
+        <v>2026-07-30T13:27:03.720Z</v>
       </c>
     </row>
     <row r="400">
@@ -7193,10 +7193,10 @@
         <v>Passed</v>
       </c>
       <c r="D400">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-30T13:10:04.515Z</v>
+        <v>2026-07-30T13:27:04.720Z</v>
       </c>
     </row>
     <row r="401">
@@ -7210,10 +7210,10 @@
         <v>Passed</v>
       </c>
       <c r="D401">
-        <v>1.51</v>
+        <v>0.13</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-30T13:10:05.515Z</v>
+        <v>2026-07-30T13:27:05.720Z</v>
       </c>
     </row>
     <row r="402">
@@ -7227,10 +7227,10 @@
         <v>Passed</v>
       </c>
       <c r="D402">
-        <v>1.06</v>
+        <v>0.78</v>
       </c>
       <c r="E402" t="str">
-        <v>2026-07-30T13:10:06.515Z</v>
+        <v>2026-07-30T13:27:06.720Z</v>
       </c>
     </row>
     <row r="403">
@@ -7244,10 +7244,10 @@
         <v>Passed</v>
       </c>
       <c r="D403">
-        <v>1.93</v>
+        <v>0.34</v>
       </c>
       <c r="E403" t="str">
-        <v>2026-07-30T13:10:07.515Z</v>
+        <v>2026-07-30T13:27:07.720Z</v>
       </c>
     </row>
     <row r="404">
@@ -7261,10 +7261,10 @@
         <v>Passed</v>
       </c>
       <c r="D404">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="E404" t="str">
-        <v>2026-07-30T13:10:08.515Z</v>
+        <v>2026-07-30T13:27:08.720Z</v>
       </c>
     </row>
     <row r="405">
@@ -7278,10 +7278,10 @@
         <v>Passed</v>
       </c>
       <c r="D405">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="E405" t="str">
-        <v>2026-07-30T13:10:09.515Z</v>
+        <v>2026-07-30T13:27:09.720Z</v>
       </c>
     </row>
     <row r="406">
@@ -7295,10 +7295,10 @@
         <v>Passed</v>
       </c>
       <c r="D406">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="E406" t="str">
-        <v>2026-07-30T13:10:10.515Z</v>
+        <v>2026-07-30T13:27:10.720Z</v>
       </c>
     </row>
     <row r="407">
@@ -7312,10 +7312,10 @@
         <v>Passed</v>
       </c>
       <c r="D407">
-        <v>0.46</v>
+        <v>1.55</v>
       </c>
       <c r="E407" t="str">
-        <v>2026-07-30T13:10:11.515Z</v>
+        <v>2026-07-30T13:27:11.720Z</v>
       </c>
     </row>
     <row r="408">
@@ -7329,10 +7329,10 @@
         <v>Passed</v>
       </c>
       <c r="D408">
-        <v>0.9</v>
+        <v>1.39</v>
       </c>
       <c r="E408" t="str">
-        <v>2026-07-30T13:10:12.515Z</v>
+        <v>2026-07-30T13:27:12.720Z</v>
       </c>
     </row>
     <row r="409">
@@ -7346,10 +7346,10 @@
         <v>Passed</v>
       </c>
       <c r="D409">
-        <v>0.29</v>
+        <v>0.69</v>
       </c>
       <c r="E409" t="str">
-        <v>2026-07-30T13:10:13.515Z</v>
+        <v>2026-07-30T13:27:13.720Z</v>
       </c>
     </row>
     <row r="410">
@@ -7363,10 +7363,10 @@
         <v>Passed</v>
       </c>
       <c r="D410">
-        <v>0.48</v>
+        <v>0.27</v>
       </c>
       <c r="E410" t="str">
-        <v>2026-07-30T13:10:14.515Z</v>
+        <v>2026-07-30T13:27:14.720Z</v>
       </c>
     </row>
     <row r="411">
@@ -7380,10 +7380,10 @@
         <v>Passed</v>
       </c>
       <c r="D411">
-        <v>0.76</v>
+        <v>0.35</v>
       </c>
       <c r="E411" t="str">
-        <v>2026-07-30T13:10:15.515Z</v>
+        <v>2026-07-30T13:27:15.720Z</v>
       </c>
     </row>
     <row r="412">
@@ -7397,10 +7397,10 @@
         <v>Passed</v>
       </c>
       <c r="D412">
-        <v>0.33</v>
+        <v>1.41</v>
       </c>
       <c r="E412" t="str">
-        <v>2026-07-30T13:10:16.515Z</v>
+        <v>2026-07-30T13:27:16.720Z</v>
       </c>
     </row>
     <row r="413">
@@ -7414,10 +7414,10 @@
         <v>Passed</v>
       </c>
       <c r="D413">
-        <v>1.86</v>
+        <v>0.43</v>
       </c>
       <c r="E413" t="str">
-        <v>2026-07-30T13:10:17.515Z</v>
+        <v>2026-07-30T13:27:17.720Z</v>
       </c>
     </row>
     <row r="414">
@@ -7431,10 +7431,10 @@
         <v>Passed</v>
       </c>
       <c r="D414">
-        <v>1.3</v>
+        <v>0.23</v>
       </c>
       <c r="E414" t="str">
-        <v>2026-07-30T13:10:18.515Z</v>
+        <v>2026-07-30T13:27:18.720Z</v>
       </c>
     </row>
     <row r="415">
@@ -7448,10 +7448,10 @@
         <v>Passed</v>
       </c>
       <c r="D415">
-        <v>0.29</v>
+        <v>0.57</v>
       </c>
       <c r="E415" t="str">
-        <v>2026-07-30T13:10:19.515Z</v>
+        <v>2026-07-30T13:27:19.720Z</v>
       </c>
     </row>
     <row r="416">
@@ -7465,10 +7465,10 @@
         <v>Passed</v>
       </c>
       <c r="D416">
-        <v>1.56</v>
+        <v>0.76</v>
       </c>
       <c r="E416" t="str">
-        <v>2026-07-30T13:10:20.515Z</v>
+        <v>2026-07-30T13:27:20.720Z</v>
       </c>
     </row>
     <row r="417">
@@ -7482,10 +7482,10 @@
         <v>Passed</v>
       </c>
       <c r="D417">
-        <v>1.75</v>
+        <v>0.94</v>
       </c>
       <c r="E417" t="str">
-        <v>2026-07-30T13:10:21.515Z</v>
+        <v>2026-07-30T13:27:21.720Z</v>
       </c>
     </row>
     <row r="418">
@@ -7499,10 +7499,10 @@
         <v>Passed</v>
       </c>
       <c r="D418">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="E418" t="str">
-        <v>2026-07-30T13:10:22.515Z</v>
+        <v>2026-07-30T13:27:22.720Z</v>
       </c>
     </row>
     <row r="419">
@@ -7516,10 +7516,10 @@
         <v>Passed</v>
       </c>
       <c r="D419">
-        <v>1.72</v>
+        <v>0.19</v>
       </c>
       <c r="E419" t="str">
-        <v>2026-07-30T13:10:23.515Z</v>
+        <v>2026-07-30T13:27:23.720Z</v>
       </c>
     </row>
     <row r="420">
@@ -7533,10 +7533,10 @@
         <v>Passed</v>
       </c>
       <c r="D420">
-        <v>1.91</v>
+        <v>0.24</v>
       </c>
       <c r="E420" t="str">
-        <v>2026-07-30T13:10:24.515Z</v>
+        <v>2026-07-30T13:27:24.720Z</v>
       </c>
     </row>
     <row r="421">
@@ -7550,10 +7550,10 @@
         <v>Passed</v>
       </c>
       <c r="D421">
-        <v>0.41</v>
+        <v>0.1</v>
       </c>
       <c r="E421" t="str">
-        <v>2026-07-30T13:10:25.515Z</v>
+        <v>2026-07-30T13:27:25.720Z</v>
       </c>
     </row>
     <row r="422">
@@ -7567,10 +7567,10 @@
         <v>Passed</v>
       </c>
       <c r="D422">
-        <v>0.62</v>
+        <v>0.32</v>
       </c>
       <c r="E422" t="str">
-        <v>2026-07-30T13:10:26.515Z</v>
+        <v>2026-07-30T13:27:26.720Z</v>
       </c>
     </row>
     <row r="423">
@@ -7584,10 +7584,10 @@
         <v>Passed</v>
       </c>
       <c r="D423">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="E423" t="str">
-        <v>2026-07-30T13:10:27.515Z</v>
+        <v>2026-07-30T13:27:27.720Z</v>
       </c>
     </row>
     <row r="424">
@@ -7601,10 +7601,10 @@
         <v>Passed</v>
       </c>
       <c r="D424">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="E424" t="str">
-        <v>2026-07-30T13:10:28.515Z</v>
+        <v>2026-07-30T13:27:28.720Z</v>
       </c>
     </row>
     <row r="425">
@@ -7618,10 +7618,10 @@
         <v>Passed</v>
       </c>
       <c r="D425">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="E425" t="str">
-        <v>2026-07-30T13:10:29.515Z</v>
+        <v>2026-07-30T13:27:29.720Z</v>
       </c>
     </row>
     <row r="426">
@@ -7635,10 +7635,10 @@
         <v>Passed</v>
       </c>
       <c r="D426">
-        <v>0.42</v>
+        <v>1.4</v>
       </c>
       <c r="E426" t="str">
-        <v>2026-07-30T13:10:30.515Z</v>
+        <v>2026-07-30T13:27:30.720Z</v>
       </c>
     </row>
     <row r="427">
@@ -7652,10 +7652,10 @@
         <v>Passed</v>
       </c>
       <c r="D427">
-        <v>0.69</v>
+        <v>1.49</v>
       </c>
       <c r="E427" t="str">
-        <v>2026-07-30T13:10:31.515Z</v>
+        <v>2026-07-30T13:27:31.720Z</v>
       </c>
     </row>
     <row r="428">
@@ -7669,10 +7669,10 @@
         <v>Passed</v>
       </c>
       <c r="D428">
-        <v>0.93</v>
+        <v>1.22</v>
       </c>
       <c r="E428" t="str">
-        <v>2026-07-30T13:10:32.515Z</v>
+        <v>2026-07-30T13:27:32.720Z</v>
       </c>
     </row>
     <row r="429">
@@ -7686,10 +7686,10 @@
         <v>Passed</v>
       </c>
       <c r="D429">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="E429" t="str">
-        <v>2026-07-30T13:10:33.515Z</v>
+        <v>2026-07-30T13:27:33.720Z</v>
       </c>
     </row>
     <row r="430">
@@ -7703,10 +7703,10 @@
         <v>Passed</v>
       </c>
       <c r="D430">
-        <v>1.52</v>
+        <v>0.39</v>
       </c>
       <c r="E430" t="str">
-        <v>2026-07-30T13:10:34.515Z</v>
+        <v>2026-07-30T13:27:34.720Z</v>
       </c>
     </row>
     <row r="431">
@@ -7720,10 +7720,10 @@
         <v>Passed</v>
       </c>
       <c r="D431">
-        <v>1.86</v>
+        <v>0.21</v>
       </c>
       <c r="E431" t="str">
-        <v>2026-07-30T13:10:35.515Z</v>
+        <v>2026-07-30T13:27:35.720Z</v>
       </c>
     </row>
     <row r="432">
@@ -7737,10 +7737,10 @@
         <v>Passed</v>
       </c>
       <c r="D432">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="E432" t="str">
-        <v>2026-07-30T13:10:36.515Z</v>
+        <v>2026-07-30T13:27:36.720Z</v>
       </c>
     </row>
     <row r="433">
@@ -7754,10 +7754,10 @@
         <v>Passed</v>
       </c>
       <c r="D433">
-        <v>0.72</v>
+        <v>1.25</v>
       </c>
       <c r="E433" t="str">
-        <v>2026-07-30T13:10:37.515Z</v>
+        <v>2026-07-30T13:27:37.720Z</v>
       </c>
     </row>
     <row r="434">
@@ -7771,10 +7771,10 @@
         <v>Passed</v>
       </c>
       <c r="D434">
-        <v>0.92</v>
+        <v>1.57</v>
       </c>
       <c r="E434" t="str">
-        <v>2026-07-30T13:10:38.515Z</v>
+        <v>2026-07-30T13:27:38.720Z</v>
       </c>
     </row>
     <row r="435">
@@ -7788,10 +7788,10 @@
         <v>Passed</v>
       </c>
       <c r="D435">
-        <v>1.57</v>
+        <v>0.06</v>
       </c>
       <c r="E435" t="str">
-        <v>2026-07-30T13:10:39.515Z</v>
+        <v>2026-07-30T13:27:39.720Z</v>
       </c>
     </row>
     <row r="436">
@@ -7805,10 +7805,10 @@
         <v>Passed</v>
       </c>
       <c r="D436">
-        <v>0.98</v>
+        <v>1.56</v>
       </c>
       <c r="E436" t="str">
-        <v>2026-07-30T13:10:40.515Z</v>
+        <v>2026-07-30T13:27:40.720Z</v>
       </c>
     </row>
     <row r="437">
@@ -7822,10 +7822,10 @@
         <v>Passed</v>
       </c>
       <c r="D437">
-        <v>1.11</v>
+        <v>0.41</v>
       </c>
       <c r="E437" t="str">
-        <v>2026-07-30T13:10:41.515Z</v>
+        <v>2026-07-30T13:27:41.720Z</v>
       </c>
     </row>
     <row r="438">
@@ -7839,10 +7839,10 @@
         <v>Passed</v>
       </c>
       <c r="D438">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="E438" t="str">
-        <v>2026-07-30T13:10:42.515Z</v>
+        <v>2026-07-30T13:27:42.720Z</v>
       </c>
     </row>
     <row r="439">
@@ -7856,10 +7856,10 @@
         <v>Passed</v>
       </c>
       <c r="D439">
-        <v>0.12</v>
+        <v>1.24</v>
       </c>
       <c r="E439" t="str">
-        <v>2026-07-30T13:10:43.515Z</v>
+        <v>2026-07-30T13:27:43.720Z</v>
       </c>
     </row>
     <row r="440">
@@ -7873,10 +7873,10 @@
         <v>Passed</v>
       </c>
       <c r="D440">
-        <v>1.24</v>
+        <v>0.37</v>
       </c>
       <c r="E440" t="str">
-        <v>2026-07-30T13:10:44.515Z</v>
+        <v>2026-07-30T13:27:44.720Z</v>
       </c>
     </row>
     <row r="441">
@@ -7890,10 +7890,10 @@
         <v>Passed</v>
       </c>
       <c r="D441">
-        <v>0.77</v>
+        <v>0.11</v>
       </c>
       <c r="E441" t="str">
-        <v>2026-07-30T13:10:45.515Z</v>
+        <v>2026-07-30T13:27:45.720Z</v>
       </c>
     </row>
     <row r="442">
@@ -7907,10 +7907,10 @@
         <v>Passed</v>
       </c>
       <c r="D442">
-        <v>1.93</v>
+        <v>0.93</v>
       </c>
       <c r="E442" t="str">
-        <v>2026-07-30T13:10:46.515Z</v>
+        <v>2026-07-30T13:27:46.720Z</v>
       </c>
     </row>
     <row r="443">
@@ -7924,10 +7924,10 @@
         <v>Passed</v>
       </c>
       <c r="D443">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="E443" t="str">
-        <v>2026-07-30T13:10:47.515Z</v>
+        <v>2026-07-30T13:27:47.720Z</v>
       </c>
     </row>
     <row r="444">
@@ -7941,10 +7941,10 @@
         <v>Passed</v>
       </c>
       <c r="D444">
-        <v>1.78</v>
+        <v>0.24</v>
       </c>
       <c r="E444" t="str">
-        <v>2026-07-30T13:10:48.515Z</v>
+        <v>2026-07-30T13:27:48.720Z</v>
       </c>
     </row>
     <row r="445">
@@ -7958,10 +7958,10 @@
         <v>Passed</v>
       </c>
       <c r="D445">
-        <v>1.58</v>
+        <v>0.71</v>
       </c>
       <c r="E445" t="str">
-        <v>2026-07-30T13:10:49.515Z</v>
+        <v>2026-07-30T13:27:49.720Z</v>
       </c>
     </row>
     <row r="446">
@@ -7975,10 +7975,10 @@
         <v>Passed</v>
       </c>
       <c r="D446">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="E446" t="str">
-        <v>2026-07-30T13:10:50.515Z</v>
+        <v>2026-07-30T13:27:50.720Z</v>
       </c>
     </row>
     <row r="447">
@@ -7992,10 +7992,10 @@
         <v>Passed</v>
       </c>
       <c r="D447">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="E447" t="str">
-        <v>2026-07-30T13:10:51.515Z</v>
+        <v>2026-07-30T13:27:51.720Z</v>
       </c>
     </row>
     <row r="448">
@@ -8012,7 +8012,7 @@
         <v>1.03</v>
       </c>
       <c r="E448" t="str">
-        <v>2026-07-30T13:10:52.515Z</v>
+        <v>2026-07-30T13:27:52.720Z</v>
       </c>
     </row>
     <row r="449">
@@ -8026,10 +8026,10 @@
         <v>Passed</v>
       </c>
       <c r="D449">
-        <v>1.76</v>
+        <v>0.45</v>
       </c>
       <c r="E449" t="str">
-        <v>2026-07-30T13:10:53.515Z</v>
+        <v>2026-07-30T13:27:53.720Z</v>
       </c>
     </row>
     <row r="450">
@@ -8043,10 +8043,10 @@
         <v>Passed</v>
       </c>
       <c r="D450">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="E450" t="str">
-        <v>2026-07-30T13:10:54.515Z</v>
+        <v>2026-07-30T13:27:54.720Z</v>
       </c>
     </row>
     <row r="451">
@@ -8060,10 +8060,10 @@
         <v>Passed</v>
       </c>
       <c r="D451">
-        <v>1.11</v>
+        <v>0.47</v>
       </c>
       <c r="E451" t="str">
-        <v>2026-07-30T13:10:55.515Z</v>
+        <v>2026-07-30T13:27:55.720Z</v>
       </c>
     </row>
     <row r="452">
@@ -8077,10 +8077,10 @@
         <v>Passed</v>
       </c>
       <c r="D452">
-        <v>0.72</v>
+        <v>1.24</v>
       </c>
       <c r="E452" t="str">
-        <v>2026-07-30T13:10:56.515Z</v>
+        <v>2026-07-30T13:27:56.720Z</v>
       </c>
     </row>
     <row r="453">
@@ -8094,10 +8094,10 @@
         <v>Passed</v>
       </c>
       <c r="D453">
-        <v>1.19</v>
+        <v>1.56</v>
       </c>
       <c r="E453" t="str">
-        <v>2026-07-30T13:10:57.515Z</v>
+        <v>2026-07-30T13:27:57.720Z</v>
       </c>
     </row>
     <row r="454">
@@ -8111,10 +8111,10 @@
         <v>Passed</v>
       </c>
       <c r="D454">
-        <v>1.96</v>
+        <v>1.36</v>
       </c>
       <c r="E454" t="str">
-        <v>2026-07-30T13:10:58.515Z</v>
+        <v>2026-07-30T13:27:58.720Z</v>
       </c>
     </row>
     <row r="455">
@@ -8128,10 +8128,10 @@
         <v>Passed</v>
       </c>
       <c r="D455">
-        <v>0.37</v>
+        <v>0.65</v>
       </c>
       <c r="E455" t="str">
-        <v>2026-07-30T13:10:59.515Z</v>
+        <v>2026-07-30T13:27:59.720Z</v>
       </c>
     </row>
     <row r="456">
@@ -8145,15 +8145,219 @@
         <v>Passed</v>
       </c>
       <c r="D456">
-        <v>1.57</v>
+        <v>0.03</v>
       </c>
       <c r="E456" t="str">
-        <v>2026-07-30T13:11:00.515Z</v>
+        <v>2026-07-30T13:28:00.720Z</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Security-TC-0456</v>
+      </c>
+      <c r="B457" t="str">
+        <v>Verify Security functionality module 456</v>
+      </c>
+      <c r="C457" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D457">
+        <v>0.68</v>
+      </c>
+      <c r="E457" t="str">
+        <v>2026-07-30T13:28:01.720Z</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>Security-TC-0457</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Verify Security functionality module 457</v>
+      </c>
+      <c r="C458" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D458">
+        <v>0.76</v>
+      </c>
+      <c r="E458" t="str">
+        <v>2026-07-30T13:28:02.720Z</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>Security-TC-0458</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Verify Security functionality module 458</v>
+      </c>
+      <c r="C459" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D459">
+        <v>0.12</v>
+      </c>
+      <c r="E459" t="str">
+        <v>2026-07-30T13:28:03.720Z</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>Security-TC-0459</v>
+      </c>
+      <c r="B460" t="str">
+        <v>Verify Security functionality module 459</v>
+      </c>
+      <c r="C460" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D460">
+        <v>0.13</v>
+      </c>
+      <c r="E460" t="str">
+        <v>2026-07-30T13:28:04.720Z</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>Security-TC-0460</v>
+      </c>
+      <c r="B461" t="str">
+        <v>Verify Security functionality module 460</v>
+      </c>
+      <c r="C461" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D461">
+        <v>1.56</v>
+      </c>
+      <c r="E461" t="str">
+        <v>2026-07-30T13:28:05.720Z</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Security-TC-0461</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Verify Security functionality module 461</v>
+      </c>
+      <c r="C462" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D462">
+        <v>1.69</v>
+      </c>
+      <c r="E462" t="str">
+        <v>2026-07-30T13:28:06.720Z</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Security-TC-0462</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Verify Security functionality module 462</v>
+      </c>
+      <c r="C463" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D463">
+        <v>1.96</v>
+      </c>
+      <c r="E463" t="str">
+        <v>2026-07-30T13:28:07.720Z</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>Security-TC-0463</v>
+      </c>
+      <c r="B464" t="str">
+        <v>Verify Security functionality module 463</v>
+      </c>
+      <c r="C464" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D464">
+        <v>1.18</v>
+      </c>
+      <c r="E464" t="str">
+        <v>2026-07-30T13:28:08.720Z</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>Security-TC-0464</v>
+      </c>
+      <c r="B465" t="str">
+        <v>Verify Security functionality module 464</v>
+      </c>
+      <c r="C465" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D465">
+        <v>1.06</v>
+      </c>
+      <c r="E465" t="str">
+        <v>2026-07-30T13:28:09.720Z</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>Security-TC-0465</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Verify Security functionality module 465</v>
+      </c>
+      <c r="C466" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D466">
+        <v>1.01</v>
+      </c>
+      <c r="E466" t="str">
+        <v>2026-07-30T13:28:10.720Z</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Security-TC-0466</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Verify Security functionality module 466</v>
+      </c>
+      <c r="C467" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D467">
+        <v>0.18</v>
+      </c>
+      <c r="E467" t="str">
+        <v>2026-07-30T13:28:11.720Z</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Security-TC-0467</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Verify Security functionality module 467</v>
+      </c>
+      <c r="C468" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D468">
+        <v>1.09</v>
+      </c>
+      <c r="E468" t="str">
+        <v>2026-07-30T13:28:12.720Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E456"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E468"/>
   </ignoredErrors>
 </worksheet>
 </file>